--- a/Mei-2026.xlsx
+++ b/Mei-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF535DF9-92BB-44C4-98DA-1D5796A5180C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EB405A-18FE-4377-AA78-28BB05D6FF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -565,16 +565,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>167</v>
+        <v>254</v>
       </c>
       <c r="C2" s="4">
-        <v>126</v>
+        <v>202</v>
       </c>
       <c r="D2" s="9">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E2" s="13">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -584,16 +584,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="C3" s="4">
-        <v>237</v>
+        <v>311</v>
       </c>
       <c r="D3" s="9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E3" s="13">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -603,16 +603,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="C4" s="4">
-        <v>149</v>
+        <v>222</v>
       </c>
       <c r="D4" s="9">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E4" s="13">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -622,7 +622,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="C5" s="4">
         <v>218</v>
@@ -631,7 +631,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="13">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -641,16 +641,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="C6" s="4">
-        <v>210</v>
+        <v>287</v>
       </c>
       <c r="D6" s="9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E6" s="13">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -660,16 +660,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C7" s="4">
-        <v>197</v>
+        <v>304</v>
       </c>
       <c r="D7" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E7" s="13">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -679,16 +679,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="C8" s="4">
-        <v>162</v>
+        <v>233</v>
       </c>
       <c r="D8" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E8" s="13">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -698,16 +698,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="C9" s="4">
-        <v>222</v>
+        <v>288</v>
       </c>
       <c r="D9" s="9">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E9" s="13">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -717,7 +717,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C10" s="4">
         <v>132</v>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
       <c r="E10" s="13">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -736,16 +736,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="C11" s="4">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="D11" s="9">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E11" s="13">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -764,7 +764,7 @@
         <v>6</v>
       </c>
       <c r="E12" s="13">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -774,16 +774,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C13" s="4">
-        <v>274</v>
+        <v>359</v>
       </c>
       <c r="D13" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="13">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -793,16 +793,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C14" s="4">
-        <v>263</v>
+        <v>350</v>
       </c>
       <c r="D14" s="9">
         <v>3</v>
       </c>
       <c r="E14" s="13">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -812,16 +812,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="C15" s="4">
-        <v>88</v>
+        <v>178</v>
       </c>
       <c r="D15" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E15" s="13">
-        <v>0.75</v>
+        <v>1.6</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -831,13 +831,13 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="C16" s="4">
-        <v>258</v>
+        <v>332</v>
       </c>
       <c r="D16" s="9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E16" s="13">
         <v>2</v>
@@ -850,16 +850,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="C17" s="4">
-        <v>245</v>
+        <v>329</v>
       </c>
       <c r="D17" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E17" s="13">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -869,16 +869,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="C18" s="4">
-        <v>149</v>
+        <v>230</v>
       </c>
       <c r="D18" s="9">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18" s="13">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -888,16 +888,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>1830</v>
+        <v>2384</v>
       </c>
       <c r="C19" s="6">
-        <v>3350</v>
+        <v>4469</v>
       </c>
       <c r="D19" s="10">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="E19" s="14">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1109,9 +1109,15 @@
       <c r="H2" s="4">
         <v>104</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
+      <c r="I2" s="4">
+        <v>113</v>
+      </c>
+      <c r="J2" s="4">
+        <v>50</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
@@ -1134,7 +1140,7 @@
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="9">
-        <v>293</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1162,9 +1168,15 @@
       <c r="H3" s="4">
         <v>106</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
+      <c r="I3" s="4">
+        <v>107</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -1187,7 +1199,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>327</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1215,9 +1227,15 @@
       <c r="H4" s="4">
         <v>0</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
+      <c r="I4" s="4">
+        <v>97</v>
+      </c>
+      <c r="J4" s="4">
+        <v>22</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -1240,7 +1258,7 @@
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="9">
-        <v>282</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1268,9 +1286,15 @@
       <c r="H5" s="4">
         <v>114</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <v>29</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
@@ -1293,7 +1317,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="9">
-        <v>370</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1321,9 +1345,15 @@
       <c r="H6" s="4">
         <v>105</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
+      <c r="I6" s="4">
+        <v>110</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
@@ -1346,7 +1376,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="9">
-        <v>334</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1374,9 +1404,15 @@
       <c r="H7" s="4">
         <v>114</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
+      <c r="I7" s="4">
+        <v>125</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
@@ -1399,7 +1435,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="9">
-        <v>274</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1427,9 +1463,15 @@
       <c r="H8" s="4">
         <v>125</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
+      <c r="I8" s="4">
+        <v>104</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
@@ -1452,7 +1494,7 @@
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="9">
-        <v>277</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1480,9 +1522,15 @@
       <c r="H9" s="4">
         <v>96</v>
       </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
+      <c r="I9" s="4">
+        <v>101</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
@@ -1505,7 +1553,7 @@
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="9">
-        <v>345</v>
+        <v>446</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1533,9 +1581,15 @@
       <c r="H10" s="4">
         <v>107</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4">
+        <v>9</v>
+      </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
@@ -1558,7 +1612,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="9">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1586,9 +1640,15 @@
       <c r="H11" s="4">
         <v>104</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
+      <c r="I11" s="4">
+        <v>95</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4">
+        <v>15</v>
+      </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
@@ -1611,7 +1671,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="9">
-        <v>243</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -1639,9 +1699,15 @@
       <c r="H12" s="4">
         <v>118</v>
       </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0</v>
+      </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
@@ -1692,9 +1758,15 @@
       <c r="H13" s="4">
         <v>117</v>
       </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
+      <c r="I13" s="4">
+        <v>101</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
@@ -1717,7 +1789,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>336</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -1745,9 +1817,15 @@
       <c r="H14" s="4">
         <v>108</v>
       </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
+      <c r="I14" s="4">
+        <v>109</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
@@ -1770,7 +1848,7 @@
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="9">
-        <v>357</v>
+        <v>466</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -1798,9 +1876,15 @@
       <c r="H15" s="4">
         <v>0</v>
       </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
+      <c r="I15" s="4">
+        <v>116</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
+        <v>26</v>
+      </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
@@ -1823,7 +1907,7 @@
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="9">
-        <v>181</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -1851,9 +1935,15 @@
       <c r="H16" s="4">
         <v>106</v>
       </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
+      <c r="I16" s="4">
+        <v>105</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
@@ -1876,7 +1966,7 @@
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="9">
-        <v>338</v>
+        <v>443</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -1904,9 +1994,15 @@
       <c r="H17" s="4">
         <v>102</v>
       </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
+      <c r="I17" s="4">
+        <v>106</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4">
+        <v>0</v>
+      </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
@@ -1929,7 +2025,7 @@
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9">
-        <v>336</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -1957,9 +2053,15 @@
       <c r="H18" s="4">
         <v>0</v>
       </c>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
+      <c r="I18" s="4">
+        <v>114</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4">
+        <v>19</v>
+      </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
@@ -1982,7 +2084,7 @@
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
       <c r="AG18" s="9">
-        <v>271</v>
+        <v>404</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2010,9 +2112,15 @@
       <c r="H19" s="6">
         <v>1526</v>
       </c>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
+      <c r="I19" s="6">
+        <v>1503</v>
+      </c>
+      <c r="J19" s="6">
+        <v>101</v>
+      </c>
+      <c r="K19" s="6">
+        <v>69</v>
+      </c>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
@@ -2035,7 +2143,7 @@
       <c r="AE19" s="6"/>
       <c r="AF19" s="6"/>
       <c r="AG19" s="10">
-        <v>5180</v>
+        <v>6853</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -2105,7 +2213,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
     </row>
   </sheetData>

--- a/Mei-2026.xlsx
+++ b/Mei-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EB405A-18FE-4377-AA78-28BB05D6FF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31218CBD-A05F-47B4-A5E4-B8CBCEFFDEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -565,18 +565,21 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="C2" s="4">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="D2" s="9">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" s="13">
-        <v>3</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="F2" s="1"/>
+      <c r="G2">
+        <v>2.4285714285714284</v>
+      </c>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -584,18 +587,21 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="C3" s="4">
-        <v>311</v>
+        <v>465</v>
       </c>
       <c r="D3" s="9">
         <v>9</v>
       </c>
       <c r="E3" s="13">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="F3" s="1"/>
+      <c r="G3">
+        <v>1.2857142857142858</v>
+      </c>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -603,18 +609,21 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>179</v>
+        <v>246</v>
       </c>
       <c r="C4" s="4">
-        <v>222</v>
+        <v>377</v>
       </c>
       <c r="D4" s="9">
         <v>17</v>
       </c>
       <c r="E4" s="13">
-        <v>3.4</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="F4" s="1"/>
+      <c r="G4">
+        <v>2.4285714285714284</v>
+      </c>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -622,18 +631,21 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>181</v>
+        <v>223</v>
       </c>
       <c r="C5" s="4">
-        <v>218</v>
+        <v>281</v>
       </c>
       <c r="D5" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="13">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="1"/>
+      <c r="G5">
+        <v>1</v>
+      </c>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -641,18 +653,21 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>157</v>
+        <v>219</v>
       </c>
       <c r="C6" s="4">
-        <v>287</v>
+        <v>448</v>
       </c>
       <c r="D6" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="13">
-        <v>1.4</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F6" s="1"/>
+      <c r="G6">
+        <v>1.1428571428571428</v>
+      </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -660,18 +675,21 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="C7" s="4">
-        <v>304</v>
+        <v>488</v>
       </c>
       <c r="D7" s="9">
         <v>10</v>
       </c>
       <c r="E7" s="13">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="F7" s="1"/>
+      <c r="G7">
+        <v>1.4285714285714286</v>
+      </c>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -679,18 +697,21 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>148</v>
+        <v>221</v>
       </c>
       <c r="C8" s="4">
-        <v>233</v>
+        <v>373</v>
       </c>
       <c r="D8" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" s="13">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1"/>
+      <c r="G8">
+        <v>1</v>
+      </c>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -698,18 +719,21 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>158</v>
+        <v>218</v>
       </c>
       <c r="C9" s="4">
-        <v>288</v>
+        <v>450</v>
       </c>
       <c r="D9" s="9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" s="13">
-        <v>3.2</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="F9" s="1"/>
+      <c r="G9">
+        <v>2.4285714285714284</v>
+      </c>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -717,18 +741,21 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="C10" s="4">
-        <v>132</v>
+        <v>283</v>
       </c>
       <c r="D10" s="9">
         <v>10</v>
       </c>
       <c r="E10" s="13">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="F10" s="1"/>
+      <c r="G10">
+        <v>1.4285714285714286</v>
+      </c>
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -736,18 +763,21 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="C11" s="4">
-        <v>247</v>
+        <v>393</v>
       </c>
       <c r="D11" s="9">
         <v>9</v>
       </c>
       <c r="E11" s="13">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="F11" s="1"/>
+      <c r="G11">
+        <v>1.2857142857142858</v>
+      </c>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -755,18 +785,21 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="C12" s="4">
-        <v>247</v>
+        <v>405</v>
       </c>
       <c r="D12" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" s="13">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="1"/>
+      <c r="G12">
+        <v>1</v>
+      </c>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -774,18 +807,21 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C13" s="4">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="D13" s="9">
         <v>7</v>
       </c>
       <c r="E13" s="13">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="F13" s="1"/>
+      <c r="G13">
+        <v>1</v>
+      </c>
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -793,18 +829,21 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="C14" s="4">
-        <v>350</v>
+        <v>491</v>
       </c>
       <c r="D14" s="9">
         <v>3</v>
       </c>
       <c r="E14" s="13">
-        <v>0.6</v>
+        <v>0.43</v>
       </c>
       <c r="F14" s="1"/>
+      <c r="G14">
+        <v>0.42857142857142855</v>
+      </c>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -812,18 +851,21 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="C15" s="4">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="D15" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="13">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="F15" s="1"/>
+      <c r="G15">
+        <v>1</v>
+      </c>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -831,18 +873,21 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>111</v>
+        <v>164</v>
       </c>
       <c r="C16" s="4">
-        <v>332</v>
+        <v>493</v>
       </c>
       <c r="D16" s="9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E16" s="13">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="F16" s="1"/>
+      <c r="G16">
+        <v>1.7142857142857142</v>
+      </c>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -850,18 +895,21 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="C17" s="4">
-        <v>329</v>
+        <v>497</v>
       </c>
       <c r="D17" s="9">
         <v>7</v>
       </c>
       <c r="E17" s="13">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="F17" s="1"/>
+      <c r="G17">
+        <v>1</v>
+      </c>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -869,18 +917,21 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="C18" s="4">
-        <v>230</v>
+        <v>305</v>
       </c>
       <c r="D18" s="9">
         <v>12</v>
       </c>
       <c r="E18" s="13">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="F18" s="1"/>
+      <c r="G18">
+        <v>1.7142857142857142</v>
+      </c>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -888,18 +939,21 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>2384</v>
+        <v>3244</v>
       </c>
       <c r="C19" s="6">
-        <v>4469</v>
+        <v>6619</v>
       </c>
       <c r="D19" s="10">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E19" s="14">
-        <v>1.86</v>
+        <v>1.39</v>
       </c>
       <c r="F19" s="1"/>
+      <c r="G19">
+        <v>1.3949579831932775</v>
+      </c>
       <c r="H19" s="1"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1118,8 +1172,12 @@
       <c r="K2" s="4">
         <v>0</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>105</v>
+      </c>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
@@ -1140,7 +1198,7 @@
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="9">
-        <v>456</v>
+        <v>561</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1177,8 +1235,12 @@
       <c r="K3" s="4">
         <v>0</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
+      <c r="L3" s="4">
+        <v>111</v>
+      </c>
+      <c r="M3" s="4">
+        <v>112</v>
+      </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
@@ -1199,7 +1261,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>434</v>
+        <v>657</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1236,8 +1298,12 @@
       <c r="K4" s="4">
         <v>0</v>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
+      <c r="L4" s="4">
+        <v>122</v>
+      </c>
+      <c r="M4" s="4">
+        <v>100</v>
+      </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
@@ -1258,7 +1324,7 @@
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="9">
-        <v>401</v>
+        <v>623</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1295,8 +1361,12 @@
       <c r="K5" s="4">
         <v>0</v>
       </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>105</v>
+      </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
@@ -1317,7 +1387,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="9">
-        <v>399</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1354,8 +1424,12 @@
       <c r="K6" s="4">
         <v>0</v>
       </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
+      <c r="L6" s="4">
+        <v>112</v>
+      </c>
+      <c r="M6" s="4">
+        <v>111</v>
+      </c>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
@@ -1376,7 +1450,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="9">
-        <v>444</v>
+        <v>667</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1413,8 +1487,12 @@
       <c r="K7" s="4">
         <v>0</v>
       </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
+      <c r="L7" s="4">
+        <v>119</v>
+      </c>
+      <c r="M7" s="4">
+        <v>131</v>
+      </c>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
@@ -1435,7 +1513,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="9">
-        <v>399</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1472,8 +1550,12 @@
       <c r="K8" s="4">
         <v>0</v>
       </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
+      <c r="L8" s="4">
+        <v>106</v>
+      </c>
+      <c r="M8" s="4">
+        <v>107</v>
+      </c>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
@@ -1494,7 +1576,7 @@
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="9">
-        <v>381</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1531,8 +1613,12 @@
       <c r="K9" s="4">
         <v>0</v>
       </c>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
+      <c r="L9" s="4">
+        <v>115</v>
+      </c>
+      <c r="M9" s="4">
+        <v>107</v>
+      </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
@@ -1553,7 +1639,7 @@
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="9">
-        <v>446</v>
+        <v>668</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1590,8 +1676,12 @@
       <c r="K10" s="4">
         <v>9</v>
       </c>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
+      <c r="L10" s="4">
+        <v>104</v>
+      </c>
+      <c r="M10" s="4">
+        <v>108</v>
+      </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
@@ -1612,7 +1702,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="9">
-        <v>250</v>
+        <v>462</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1649,8 +1739,12 @@
       <c r="K11" s="4">
         <v>15</v>
       </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
+      <c r="L11" s="4">
+        <v>76</v>
+      </c>
+      <c r="M11" s="4">
+        <v>114</v>
+      </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
@@ -1671,7 +1765,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="9">
-        <v>353</v>
+        <v>543</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -1708,8 +1802,12 @@
       <c r="K12" s="4">
         <v>0</v>
       </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
+      <c r="L12" s="4">
+        <v>103</v>
+      </c>
+      <c r="M12" s="4">
+        <v>116</v>
+      </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
@@ -1730,7 +1828,7 @@
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="9">
-        <v>375</v>
+        <v>594</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -1767,8 +1865,12 @@
       <c r="K13" s="4">
         <v>0</v>
       </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
+      <c r="L13" s="4">
+        <v>28</v>
+      </c>
+      <c r="M13" s="4">
+        <v>0</v>
+      </c>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
@@ -1789,7 +1891,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>437</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -1826,8 +1928,12 @@
       <c r="K14" s="4">
         <v>0</v>
       </c>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
+      <c r="L14" s="4">
+        <v>72</v>
+      </c>
+      <c r="M14" s="4">
+        <v>112</v>
+      </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
@@ -1848,7 +1954,7 @@
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="9">
-        <v>466</v>
+        <v>650</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -1885,8 +1991,12 @@
       <c r="K15" s="4">
         <v>26</v>
       </c>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
+      <c r="L15" s="4">
+        <v>74</v>
+      </c>
+      <c r="M15" s="4">
+        <v>3</v>
+      </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
@@ -1907,7 +2017,7 @@
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="9">
-        <v>323</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -1944,8 +2054,12 @@
       <c r="K16" s="4">
         <v>0</v>
       </c>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
+      <c r="L16" s="4">
+        <v>105</v>
+      </c>
+      <c r="M16" s="4">
+        <v>109</v>
+      </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
@@ -1966,7 +2080,7 @@
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="9">
-        <v>443</v>
+        <v>657</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -2003,8 +2117,12 @@
       <c r="K17" s="4">
         <v>0</v>
       </c>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
+      <c r="L17" s="4">
+        <v>106</v>
+      </c>
+      <c r="M17" s="4">
+        <v>108</v>
+      </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
@@ -2025,7 +2143,7 @@
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9">
-        <v>442</v>
+        <v>656</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -2062,8 +2180,12 @@
       <c r="K18" s="4">
         <v>19</v>
       </c>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
+      <c r="L18" s="4">
+        <v>109</v>
+      </c>
+      <c r="M18" s="4">
+        <v>0</v>
+      </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
@@ -2084,7 +2206,7 @@
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
       <c r="AG18" s="9">
-        <v>404</v>
+        <v>513</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2121,8 +2243,12 @@
       <c r="K19" s="6">
         <v>69</v>
       </c>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="L19" s="6">
+        <v>1462</v>
+      </c>
+      <c r="M19" s="6">
+        <v>1548</v>
+      </c>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
@@ -2143,7 +2269,7 @@
       <c r="AE19" s="6"/>
       <c r="AF19" s="6"/>
       <c r="AG19" s="10">
-        <v>6853</v>
+        <v>9863</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -2213,7 +2339,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>1.86</v>
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Mei-2026.xlsx
+++ b/Mei-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31218CBD-A05F-47B4-A5E4-B8CBCEFFDEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967C65DB-9C74-4BD9-A7EF-42FDEBCEC1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -571,15 +571,12 @@
         <v>269</v>
       </c>
       <c r="D2" s="9">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E2" s="13">
-        <v>2.4300000000000002</v>
+        <v>3.43</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="G2">
-        <v>2.4285714285714284</v>
-      </c>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -593,15 +590,12 @@
         <v>465</v>
       </c>
       <c r="D3" s="9">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" s="13">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3">
-        <v>1.2857142857142858</v>
-      </c>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -615,15 +609,12 @@
         <v>377</v>
       </c>
       <c r="D4" s="9">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E4" s="13">
-        <v>2.4300000000000002</v>
+        <v>3.71</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4">
-        <v>2.4285714285714284</v>
-      </c>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -637,15 +628,12 @@
         <v>281</v>
       </c>
       <c r="D5" s="9">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E5" s="13">
-        <v>1</v>
+        <v>1.57</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5">
-        <v>1</v>
-      </c>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -659,15 +647,12 @@
         <v>448</v>
       </c>
       <c r="D6" s="9">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E6" s="13">
-        <v>1.1399999999999999</v>
+        <v>3.14</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6">
-        <v>1.1428571428571428</v>
-      </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -681,15 +666,12 @@
         <v>488</v>
       </c>
       <c r="D7" s="9">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E7" s="13">
-        <v>1.43</v>
+        <v>1.86</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7">
-        <v>1.4285714285714286</v>
-      </c>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -703,15 +685,12 @@
         <v>373</v>
       </c>
       <c r="D8" s="9">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E8" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8">
-        <v>1</v>
-      </c>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -725,15 +704,12 @@
         <v>450</v>
       </c>
       <c r="D9" s="9">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E9" s="13">
-        <v>2.4300000000000002</v>
+        <v>3.71</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9">
-        <v>2.4285714285714284</v>
-      </c>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -747,15 +723,12 @@
         <v>283</v>
       </c>
       <c r="D10" s="9">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E10" s="13">
-        <v>1.43</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10">
-        <v>1.4285714285714286</v>
-      </c>
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,15 +742,12 @@
         <v>393</v>
       </c>
       <c r="D11" s="9">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E11" s="13">
-        <v>1.29</v>
+        <v>2.14</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11">
-        <v>1.2857142857142858</v>
-      </c>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -791,15 +761,12 @@
         <v>405</v>
       </c>
       <c r="D12" s="9">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E12" s="13">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12">
-        <v>1</v>
-      </c>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -813,15 +780,12 @@
         <v>376</v>
       </c>
       <c r="D13" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E13" s="13">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13">
-        <v>1</v>
-      </c>
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -835,15 +799,12 @@
         <v>491</v>
       </c>
       <c r="D14" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E14" s="13">
-        <v>0.43</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14">
-        <v>0.42857142857142855</v>
-      </c>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -857,15 +818,12 @@
         <v>225</v>
       </c>
       <c r="D15" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E15" s="13">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15">
-        <v>1</v>
-      </c>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -879,15 +837,12 @@
         <v>493</v>
       </c>
       <c r="D16" s="9">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E16" s="13">
-        <v>1.71</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16">
-        <v>1.7142857142857142</v>
-      </c>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -901,15 +856,12 @@
         <v>497</v>
       </c>
       <c r="D17" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E17" s="13">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="G17">
-        <v>1</v>
-      </c>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -923,15 +875,12 @@
         <v>305</v>
       </c>
       <c r="D18" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E18" s="13">
-        <v>1.71</v>
+        <v>2.57</v>
       </c>
       <c r="F18" s="1"/>
-      <c r="G18">
-        <v>1.7142857142857142</v>
-      </c>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -945,15 +894,12 @@
         <v>6619</v>
       </c>
       <c r="D19" s="10">
-        <v>166</v>
+        <v>267</v>
       </c>
       <c r="E19" s="14">
-        <v>1.39</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="F19" s="1"/>
-      <c r="G19">
-        <v>1.3949579831932775</v>
-      </c>
       <c r="H19" s="1"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -2339,7 +2285,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>1.39</v>
+        <v>2.2400000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/Mei-2026.xlsx
+++ b/Mei-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967C65DB-9C74-4BD9-A7EF-42FDEBCEC1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1D5D24-4B33-4906-B2BD-373A2A433409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -565,16 +565,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="C2" s="4">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="D2" s="9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" s="13">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -584,16 +584,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="C3" s="4">
-        <v>465</v>
+        <v>538</v>
       </c>
       <c r="D3" s="9">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" s="13">
-        <v>1.57</v>
+        <v>1.625</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -603,16 +603,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C4" s="4">
         <v>377</v>
       </c>
       <c r="D4" s="9">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E4" s="13">
-        <v>3.71</v>
+        <v>4.125</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -622,16 +622,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="C5" s="4">
-        <v>281</v>
+        <v>353</v>
       </c>
       <c r="D5" s="9">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E5" s="13">
-        <v>1.57</v>
+        <v>1.875</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -641,16 +641,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="C6" s="4">
-        <v>448</v>
+        <v>534</v>
       </c>
       <c r="D6" s="9">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6" s="13">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -660,16 +660,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="C7" s="4">
-        <v>488</v>
+        <v>579</v>
       </c>
       <c r="D7" s="9">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" s="13">
-        <v>1.86</v>
+        <v>1.875</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -679,16 +679,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="C8" s="4">
-        <v>373</v>
+        <v>438</v>
       </c>
       <c r="D8" s="9">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E8" s="13">
-        <v>2</v>
+        <v>2.625</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -698,16 +698,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C9" s="4">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D9" s="9">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E9" s="13">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -723,10 +723,10 @@
         <v>283</v>
       </c>
       <c r="D10" s="9">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E10" s="13">
-        <v>2.4300000000000002</v>
+        <v>2.5</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -736,16 +736,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C11" s="4">
-        <v>393</v>
+        <v>426</v>
       </c>
       <c r="D11" s="9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E11" s="13">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -755,16 +755,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="C12" s="4">
-        <v>405</v>
+        <v>492</v>
       </c>
       <c r="D12" s="9">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E12" s="13">
-        <v>2.14</v>
+        <v>2.375</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -774,16 +774,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C13" s="4">
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="D13" s="9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E13" s="13">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -793,16 +793,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="C14" s="4">
-        <v>491</v>
+        <v>571</v>
       </c>
       <c r="D14" s="9">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E14" s="13">
-        <v>1.1399999999999999</v>
+        <v>1.625</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -812,16 +812,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="C15" s="4">
-        <v>225</v>
+        <v>306</v>
       </c>
       <c r="D15" s="9">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E15" s="13">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -831,16 +831,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="C16" s="4">
-        <v>493</v>
+        <v>574</v>
       </c>
       <c r="D16" s="9">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E16" s="13">
-        <v>2.4300000000000002</v>
+        <v>2.625</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -850,16 +850,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="C17" s="4">
-        <v>497</v>
+        <v>566</v>
       </c>
       <c r="D17" s="9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E17" s="13">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -869,16 +869,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="C18" s="4">
-        <v>305</v>
+        <v>393</v>
       </c>
       <c r="D18" s="9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E18" s="13">
-        <v>2.57</v>
+        <v>2.625</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -888,16 +888,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>3244</v>
+        <v>3546</v>
       </c>
       <c r="C19" s="6">
-        <v>6619</v>
+        <v>7644</v>
       </c>
       <c r="D19" s="10">
-        <v>267</v>
+        <v>323</v>
       </c>
       <c r="E19" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.375</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1124,7 +1124,9 @@
       <c r="M2" s="4">
         <v>105</v>
       </c>
-      <c r="N2" s="4"/>
+      <c r="N2" s="4">
+        <v>76</v>
+      </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
@@ -1144,7 +1146,7 @@
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="9">
-        <v>561</v>
+        <v>637</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1187,7 +1189,9 @@
       <c r="M3" s="4">
         <v>112</v>
       </c>
-      <c r="N3" s="4"/>
+      <c r="N3" s="4">
+        <v>93</v>
+      </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
@@ -1207,7 +1211,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>657</v>
+        <v>750</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1250,7 +1254,9 @@
       <c r="M4" s="4">
         <v>100</v>
       </c>
-      <c r="N4" s="4"/>
+      <c r="N4" s="4">
+        <v>2</v>
+      </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
@@ -1270,7 +1276,7 @@
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="9">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1313,7 +1319,9 @@
       <c r="M5" s="4">
         <v>105</v>
       </c>
-      <c r="N5" s="4"/>
+      <c r="N5" s="4">
+        <v>96</v>
+      </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
@@ -1333,7 +1341,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="9">
-        <v>504</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1376,7 +1384,9 @@
       <c r="M6" s="4">
         <v>111</v>
       </c>
-      <c r="N6" s="4"/>
+      <c r="N6" s="4">
+        <v>104</v>
+      </c>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
@@ -1396,7 +1406,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="9">
-        <v>667</v>
+        <v>771</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1439,7 +1449,9 @@
       <c r="M7" s="4">
         <v>131</v>
       </c>
-      <c r="N7" s="4"/>
+      <c r="N7" s="4">
+        <v>118</v>
+      </c>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
@@ -1459,7 +1471,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="9">
-        <v>649</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1502,7 +1514,9 @@
       <c r="M8" s="4">
         <v>107</v>
       </c>
-      <c r="N8" s="4"/>
+      <c r="N8" s="4">
+        <v>96</v>
+      </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
@@ -1522,7 +1536,7 @@
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="9">
-        <v>594</v>
+        <v>690</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1565,7 +1579,9 @@
       <c r="M9" s="4">
         <v>107</v>
       </c>
-      <c r="N9" s="4"/>
+      <c r="N9" s="4">
+        <v>13</v>
+      </c>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
@@ -1585,7 +1601,7 @@
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="9">
-        <v>668</v>
+        <v>681</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1628,7 +1644,9 @@
       <c r="M10" s="4">
         <v>108</v>
       </c>
-      <c r="N10" s="4"/>
+      <c r="N10" s="4">
+        <v>0</v>
+      </c>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
@@ -1691,7 +1709,9 @@
       <c r="M11" s="4">
         <v>114</v>
       </c>
-      <c r="N11" s="4"/>
+      <c r="N11" s="4">
+        <v>49</v>
+      </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
@@ -1711,7 +1731,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="9">
-        <v>543</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -1754,7 +1774,9 @@
       <c r="M12" s="4">
         <v>116</v>
       </c>
-      <c r="N12" s="4"/>
+      <c r="N12" s="4">
+        <v>112</v>
+      </c>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
@@ -1774,7 +1796,7 @@
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="9">
-        <v>594</v>
+        <v>706</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -1817,7 +1839,9 @@
       <c r="M13" s="4">
         <v>0</v>
       </c>
-      <c r="N13" s="4"/>
+      <c r="N13" s="4">
+        <v>72</v>
+      </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
@@ -1837,7 +1861,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>465</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -1880,7 +1904,9 @@
       <c r="M14" s="4">
         <v>112</v>
       </c>
-      <c r="N14" s="4"/>
+      <c r="N14" s="4">
+        <v>96</v>
+      </c>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
@@ -1900,7 +1926,7 @@
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="9">
-        <v>650</v>
+        <v>746</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -1943,7 +1969,9 @@
       <c r="M15" s="4">
         <v>3</v>
       </c>
-      <c r="N15" s="4"/>
+      <c r="N15" s="4">
+        <v>109</v>
+      </c>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
@@ -1963,7 +1991,7 @@
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="9">
-        <v>400</v>
+        <v>509</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -2006,7 +2034,9 @@
       <c r="M16" s="4">
         <v>109</v>
       </c>
-      <c r="N16" s="4"/>
+      <c r="N16" s="4">
+        <v>99</v>
+      </c>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
@@ -2026,7 +2056,7 @@
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="9">
-        <v>657</v>
+        <v>756</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -2069,7 +2099,9 @@
       <c r="M17" s="4">
         <v>108</v>
       </c>
-      <c r="N17" s="4"/>
+      <c r="N17" s="4">
+        <v>83</v>
+      </c>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
@@ -2089,7 +2121,7 @@
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9">
-        <v>656</v>
+        <v>739</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -2132,7 +2164,9 @@
       <c r="M18" s="4">
         <v>0</v>
       </c>
-      <c r="N18" s="4"/>
+      <c r="N18" s="4">
+        <v>109</v>
+      </c>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
@@ -2152,7 +2186,7 @@
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
       <c r="AG18" s="9">
-        <v>513</v>
+        <v>622</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2195,7 +2229,9 @@
       <c r="M19" s="6">
         <v>1548</v>
       </c>
-      <c r="N19" s="6"/>
+      <c r="N19" s="6">
+        <v>1327</v>
+      </c>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
@@ -2215,7 +2251,7 @@
       <c r="AE19" s="6"/>
       <c r="AF19" s="6"/>
       <c r="AG19" s="10">
-        <v>9863</v>
+        <v>11190</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -2285,7 +2321,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.375</v>
       </c>
     </row>
   </sheetData>

--- a/Mei-2026.xlsx
+++ b/Mei-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1D5D24-4B33-4906-B2BD-373A2A433409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C111857B-AF37-4559-9DEB-93183A068EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -565,18 +565,21 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>307</v>
+        <v>372</v>
       </c>
       <c r="C2" s="4">
-        <v>330</v>
+        <v>399</v>
       </c>
       <c r="D2" s="9">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E2" s="13">
-        <v>3.25</v>
+        <v>3.5555555555555554</v>
       </c>
       <c r="F2" s="1"/>
+      <c r="G2">
+        <v>3.5555555555555554</v>
+      </c>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -584,18 +587,21 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="C3" s="4">
-        <v>538</v>
+        <v>599</v>
       </c>
       <c r="D3" s="9">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="13">
-        <v>1.625</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="F3" s="1"/>
+      <c r="G3">
+        <v>1.6666666666666667</v>
+      </c>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -603,18 +609,21 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="C4" s="4">
         <v>377</v>
       </c>
       <c r="D4" s="9">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E4" s="13">
-        <v>4.125</v>
+        <v>3.3333333333333335</v>
       </c>
       <c r="F4" s="1"/>
+      <c r="G4">
+        <v>3.3333333333333335</v>
+      </c>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -622,18 +631,21 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>247</v>
+        <v>303</v>
       </c>
       <c r="C5" s="4">
-        <v>353</v>
+        <v>418</v>
       </c>
       <c r="D5" s="9">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E5" s="13">
-        <v>1.875</v>
+        <v>2.1111111111111112</v>
       </c>
       <c r="F5" s="1"/>
+      <c r="G5">
+        <v>2.1111111111111112</v>
+      </c>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -641,18 +653,21 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="C6" s="4">
-        <v>534</v>
+        <v>618</v>
       </c>
       <c r="D6" s="9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6" s="13">
-        <v>3</v>
+        <v>2.8888888888888888</v>
       </c>
       <c r="F6" s="1"/>
+      <c r="G6">
+        <v>2.8888888888888888</v>
+      </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -660,18 +675,21 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>188</v>
+        <v>221</v>
       </c>
       <c r="C7" s="4">
-        <v>579</v>
+        <v>678</v>
       </c>
       <c r="D7" s="9">
         <v>15</v>
       </c>
       <c r="E7" s="13">
-        <v>1.875</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="F7" s="1"/>
+      <c r="G7">
+        <v>1.6666666666666667</v>
+      </c>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -685,12 +703,15 @@
         <v>438</v>
       </c>
       <c r="D8" s="9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E8" s="13">
-        <v>2.625</v>
+        <v>2.5555555555555554</v>
       </c>
       <c r="F8" s="1"/>
+      <c r="G8">
+        <v>2.5555555555555554</v>
+      </c>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -704,12 +725,15 @@
         <v>451</v>
       </c>
       <c r="D9" s="9">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E9" s="13">
-        <v>3.5</v>
+        <v>3.4444444444444446</v>
       </c>
       <c r="F9" s="1"/>
+      <c r="G9">
+        <v>3.4444444444444446</v>
+      </c>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -717,18 +741,21 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="C10" s="4">
-        <v>283</v>
+        <v>350</v>
       </c>
       <c r="D10" s="9">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E10" s="13">
-        <v>2.5</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="F10" s="1"/>
+      <c r="G10">
+        <v>2.6666666666666665</v>
+      </c>
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -736,18 +763,21 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="C11" s="4">
-        <v>426</v>
+        <v>498</v>
       </c>
       <c r="D11" s="9">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E11" s="13">
         <v>2</v>
       </c>
       <c r="F11" s="1"/>
+      <c r="G11">
+        <v>2</v>
+      </c>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -755,18 +785,21 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="C12" s="4">
-        <v>492</v>
+        <v>579</v>
       </c>
       <c r="D12" s="9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" s="13">
-        <v>2.375</v>
+        <v>2.2222222222222223</v>
       </c>
       <c r="F12" s="1"/>
+      <c r="G12">
+        <v>2.2222222222222223</v>
+      </c>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -774,18 +807,21 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C13" s="4">
-        <v>433</v>
+        <v>515</v>
       </c>
       <c r="D13" s="9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13" s="13">
-        <v>1.5</v>
+        <v>1.5555555555555556</v>
       </c>
       <c r="F13" s="1"/>
+      <c r="G13">
+        <v>1.5555555555555556</v>
+      </c>
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -793,18 +829,21 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C14" s="4">
-        <v>571</v>
+        <v>647</v>
       </c>
       <c r="D14" s="9">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E14" s="13">
-        <v>1.625</v>
+        <v>2.4444444444444446</v>
       </c>
       <c r="F14" s="1"/>
+      <c r="G14">
+        <v>2.4444444444444446</v>
+      </c>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -812,18 +851,21 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>203</v>
+        <v>267</v>
       </c>
       <c r="C15" s="4">
-        <v>306</v>
+        <v>393</v>
       </c>
       <c r="D15" s="9">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E15" s="13">
-        <v>1.75</v>
+        <v>2.1111111111111112</v>
       </c>
       <c r="F15" s="1"/>
+      <c r="G15">
+        <v>2.1111111111111112</v>
+      </c>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -831,18 +873,21 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="C16" s="4">
-        <v>574</v>
+        <v>652</v>
       </c>
       <c r="D16" s="9">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E16" s="13">
-        <v>2.625</v>
+        <v>2.8888888888888888</v>
       </c>
       <c r="F16" s="1"/>
+      <c r="G16">
+        <v>2.8888888888888888</v>
+      </c>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -856,12 +901,15 @@
         <v>566</v>
       </c>
       <c r="D17" s="9">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E17" s="13">
-        <v>1.5</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="F17" s="1"/>
+      <c r="G17">
+        <v>1.6666666666666667</v>
+      </c>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -869,18 +917,21 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="C18" s="4">
-        <v>393</v>
+        <v>473</v>
       </c>
       <c r="D18" s="9">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E18" s="13">
-        <v>2.625</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="F18" s="1"/>
+      <c r="G18">
+        <v>2.6666666666666665</v>
+      </c>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -888,18 +939,21 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>3546</v>
+        <v>4062</v>
       </c>
       <c r="C19" s="6">
-        <v>7644</v>
+        <v>8651</v>
       </c>
       <c r="D19" s="10">
-        <v>323</v>
+        <v>373</v>
       </c>
       <c r="E19" s="14">
-        <v>2.375</v>
+        <v>2.4379084967320259</v>
       </c>
       <c r="F19" s="1"/>
+      <c r="G19">
+        <v>2.4379084967320259</v>
+      </c>
       <c r="H19" s="1"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1128,9 +1182,15 @@
         <v>76</v>
       </c>
       <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
+      <c r="P2" s="4">
+        <v>103</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>31</v>
+      </c>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
@@ -1146,7 +1206,7 @@
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="9">
-        <v>637</v>
+        <v>771</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1193,9 +1253,15 @@
         <v>93</v>
       </c>
       <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
+      <c r="P3" s="4">
+        <v>85</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4">
+        <v>0</v>
+      </c>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
@@ -1211,7 +1277,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>750</v>
+        <v>835</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1258,9 +1324,15 @@
         <v>2</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
+      <c r="P4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>34</v>
+      </c>
+      <c r="R4" s="4">
+        <v>25</v>
+      </c>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
@@ -1276,7 +1348,7 @@
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="9">
-        <v>625</v>
+        <v>684</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1323,9 +1395,15 @@
         <v>96</v>
       </c>
       <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
+      <c r="P5" s="4">
+        <v>98</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4">
+        <v>23</v>
+      </c>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
@@ -1341,7 +1419,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="9">
-        <v>600</v>
+        <v>721</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1388,9 +1466,15 @@
         <v>104</v>
       </c>
       <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
+      <c r="P6" s="4">
+        <v>108</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0</v>
+      </c>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
@@ -1406,7 +1490,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="9">
-        <v>771</v>
+        <v>879</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1453,9 +1537,15 @@
         <v>118</v>
       </c>
       <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
+      <c r="P7" s="4">
+        <v>132</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4">
+        <v>0</v>
+      </c>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
@@ -1471,7 +1561,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="9">
-        <v>767</v>
+        <v>899</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1518,9 +1608,15 @@
         <v>96</v>
       </c>
       <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4">
+        <v>0</v>
+      </c>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
@@ -1583,9 +1679,15 @@
         <v>13</v>
       </c>
       <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
+      <c r="P9" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4">
+        <v>0</v>
+      </c>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
@@ -1648,9 +1750,15 @@
         <v>0</v>
       </c>
       <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
+      <c r="P10" s="4">
+        <v>99</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>4</v>
+      </c>
+      <c r="R10" s="4">
+        <v>0</v>
+      </c>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
@@ -1666,7 +1774,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="9">
-        <v>462</v>
+        <v>565</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1713,9 +1821,15 @@
         <v>49</v>
       </c>
       <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
+      <c r="P11" s="4">
+        <v>85</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0</v>
+      </c>
+      <c r="R11" s="4">
+        <v>0</v>
+      </c>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
@@ -1731,7 +1845,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="9">
-        <v>592</v>
+        <v>677</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -1778,9 +1892,15 @@
         <v>112</v>
       </c>
       <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
+      <c r="P12" s="4">
+        <v>116</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0</v>
+      </c>
+      <c r="R12" s="4">
+        <v>0</v>
+      </c>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
@@ -1796,7 +1916,7 @@
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="9">
-        <v>706</v>
+        <v>822</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -1843,9 +1963,15 @@
         <v>72</v>
       </c>
       <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
+      <c r="P13" s="4">
+        <v>97</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4">
+        <v>0</v>
+      </c>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
@@ -1861,7 +1987,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>537</v>
+        <v>634</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -1908,9 +2034,15 @@
         <v>96</v>
       </c>
       <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
+      <c r="P14" s="4">
+        <v>107</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4">
+        <v>0</v>
+      </c>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
@@ -1926,7 +2058,7 @@
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="9">
-        <v>746</v>
+        <v>853</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -1973,9 +2105,15 @@
         <v>109</v>
       </c>
       <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
+      <c r="P15" s="4">
+        <v>115</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>36</v>
+      </c>
+      <c r="R15" s="4">
+        <v>0</v>
+      </c>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
@@ -1991,7 +2129,7 @@
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="9">
-        <v>509</v>
+        <v>660</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -2038,9 +2176,15 @@
         <v>99</v>
       </c>
       <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
+      <c r="P16" s="4">
+        <v>101</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>0</v>
+      </c>
+      <c r="R16" s="4">
+        <v>0</v>
+      </c>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
@@ -2056,7 +2200,7 @@
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="9">
-        <v>756</v>
+        <v>857</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -2103,9 +2247,15 @@
         <v>83</v>
       </c>
       <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
+      <c r="P17" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>0</v>
+      </c>
+      <c r="R17" s="4">
+        <v>0</v>
+      </c>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
       <c r="U17" s="4"/>
@@ -2168,9 +2318,15 @@
         <v>109</v>
       </c>
       <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4"/>
+      <c r="P18" s="4">
+        <v>100</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>24</v>
+      </c>
+      <c r="R18" s="4">
+        <v>0</v>
+      </c>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
       <c r="U18" s="4"/>
@@ -2186,7 +2342,7 @@
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
       <c r="AG18" s="9">
-        <v>622</v>
+        <v>746</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2233,9 +2389,15 @@
         <v>1327</v>
       </c>
       <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
+      <c r="P19" s="6">
+        <v>1346</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>98</v>
+      </c>
+      <c r="R19" s="6">
+        <v>79</v>
+      </c>
       <c r="S19" s="6"/>
       <c r="T19" s="6"/>
       <c r="U19" s="6"/>
@@ -2251,7 +2413,7 @@
       <c r="AE19" s="6"/>
       <c r="AF19" s="6"/>
       <c r="AG19" s="10">
-        <v>11190</v>
+        <v>12713</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -2321,7 +2483,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.375</v>
+        <v>2.4379084967320259</v>
       </c>
     </row>
   </sheetData>

--- a/Mei-2026.xlsx
+++ b/Mei-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C111857B-AF37-4559-9DEB-93183A068EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5613829-736F-483E-AAF2-DDC462FB8406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -565,21 +565,18 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>372</v>
+        <v>436</v>
       </c>
       <c r="C2" s="4">
-        <v>399</v>
+        <v>538</v>
       </c>
       <c r="D2" s="9">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E2" s="13">
-        <v>3.5555555555555554</v>
+        <v>3.9090909090909092</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="G2">
-        <v>3.5555555555555554</v>
-      </c>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -587,21 +584,18 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>236</v>
+        <v>306</v>
       </c>
       <c r="C3" s="4">
-        <v>599</v>
+        <v>740</v>
       </c>
       <c r="D3" s="9">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E3" s="13">
-        <v>1.6666666666666667</v>
+        <v>2</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3">
-        <v>1.6666666666666667</v>
-      </c>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -609,21 +603,18 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>307</v>
+        <v>346</v>
       </c>
       <c r="C4" s="4">
-        <v>377</v>
+        <v>446</v>
       </c>
       <c r="D4" s="9">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E4" s="13">
-        <v>3.3333333333333335</v>
+        <v>3.4545454545454546</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4">
-        <v>3.3333333333333335</v>
-      </c>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -631,21 +622,18 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>303</v>
+        <v>345</v>
       </c>
       <c r="C5" s="4">
-        <v>418</v>
+        <v>490</v>
       </c>
       <c r="D5" s="9">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E5" s="13">
-        <v>2.1111111111111112</v>
+        <v>2.3636363636363638</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5">
-        <v>2.1111111111111112</v>
-      </c>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -653,21 +641,18 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>261</v>
+        <v>323</v>
       </c>
       <c r="C6" s="4">
-        <v>618</v>
+        <v>783</v>
       </c>
       <c r="D6" s="9">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E6" s="13">
-        <v>2.8888888888888888</v>
+        <v>2.6363636363636362</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6">
-        <v>2.8888888888888888</v>
-      </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -675,21 +660,18 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>221</v>
+        <v>290</v>
       </c>
       <c r="C7" s="4">
-        <v>678</v>
+        <v>771</v>
       </c>
       <c r="D7" s="9">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E7" s="13">
-        <v>1.6666666666666667</v>
+        <v>2.0909090909090908</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7">
-        <v>1.6666666666666667</v>
-      </c>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -697,21 +679,18 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>252</v>
+        <v>291</v>
       </c>
       <c r="C8" s="4">
-        <v>438</v>
+        <v>510</v>
       </c>
       <c r="D8" s="9">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E8" s="13">
-        <v>2.5555555555555554</v>
+        <v>2.2727272727272729</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8">
-        <v>2.5555555555555554</v>
-      </c>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -719,21 +698,18 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>230</v>
+        <v>304</v>
       </c>
       <c r="C9" s="4">
-        <v>451</v>
+        <v>587</v>
       </c>
       <c r="D9" s="9">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E9" s="13">
-        <v>3.4444444444444446</v>
+        <v>3.4545454545454546</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9">
-        <v>3.4444444444444446</v>
-      </c>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -741,21 +717,18 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>215</v>
+        <v>258</v>
       </c>
       <c r="C10" s="4">
-        <v>350</v>
+        <v>415</v>
       </c>
       <c r="D10" s="9">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E10" s="13">
-        <v>2.6666666666666665</v>
+        <v>3.1818181818181817</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10">
-        <v>2.6666666666666665</v>
-      </c>
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -763,21 +736,18 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>179</v>
+        <v>230</v>
       </c>
       <c r="C11" s="4">
-        <v>498</v>
+        <v>668</v>
       </c>
       <c r="D11" s="9">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E11" s="13">
-        <v>2</v>
+        <v>1.8181818181818181</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11">
-        <v>2</v>
-      </c>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -785,21 +755,18 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>243</v>
+        <v>299</v>
       </c>
       <c r="C12" s="4">
-        <v>579</v>
+        <v>647</v>
       </c>
       <c r="D12" s="9">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E12" s="13">
-        <v>2.2222222222222223</v>
+        <v>2.1818181818181817</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12">
-        <v>2.2222222222222223</v>
-      </c>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -807,21 +774,18 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>119</v>
+        <v>167</v>
       </c>
       <c r="C13" s="4">
-        <v>515</v>
+        <v>685</v>
       </c>
       <c r="D13" s="9">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E13" s="13">
-        <v>1.5555555555555556</v>
+        <v>1.7272727272727273</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13">
-        <v>1.5555555555555556</v>
-      </c>
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -829,21 +793,18 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>206</v>
+        <v>258</v>
       </c>
       <c r="C14" s="4">
-        <v>647</v>
+        <v>817</v>
       </c>
       <c r="D14" s="9">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E14" s="13">
-        <v>2.4444444444444446</v>
+        <v>2.4545454545454546</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14">
-        <v>2.4444444444444446</v>
-      </c>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -851,21 +812,18 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="C15" s="4">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="D15" s="9">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E15" s="13">
-        <v>2.1111111111111112</v>
+        <v>2.2727272727272729</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15">
-        <v>2.1111111111111112</v>
-      </c>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,21 +831,18 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>205</v>
+        <v>268</v>
       </c>
       <c r="C16" s="4">
-        <v>652</v>
+        <v>808</v>
       </c>
       <c r="D16" s="9">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E16" s="13">
-        <v>2.8888888888888888</v>
+        <v>2.9090909090909092</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16">
-        <v>2.8888888888888888</v>
-      </c>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -895,21 +850,18 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>173</v>
+        <v>231</v>
       </c>
       <c r="C17" s="4">
-        <v>566</v>
+        <v>719</v>
       </c>
       <c r="D17" s="9">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E17" s="13">
-        <v>1.6666666666666667</v>
+        <v>1.6363636363636365</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="G17">
-        <v>1.6666666666666667</v>
-      </c>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -917,21 +869,18 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="C18" s="4">
-        <v>473</v>
+        <v>548</v>
       </c>
       <c r="D18" s="9">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E18" s="13">
-        <v>2.6666666666666665</v>
+        <v>2.6363636363636362</v>
       </c>
       <c r="F18" s="1"/>
-      <c r="G18">
-        <v>2.6666666666666665</v>
-      </c>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -939,21 +888,18 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>4062</v>
+        <v>4956</v>
       </c>
       <c r="C19" s="6">
-        <v>8651</v>
+        <v>10600</v>
       </c>
       <c r="D19" s="10">
-        <v>373</v>
+        <v>473</v>
       </c>
       <c r="E19" s="14">
-        <v>2.4379084967320259</v>
+        <v>2.5294117647058822</v>
       </c>
       <c r="F19" s="1"/>
-      <c r="G19">
-        <v>2.4379084967320259</v>
-      </c>
       <c r="H19" s="1"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1191,8 +1137,12 @@
       <c r="R2" s="4">
         <v>31</v>
       </c>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
+      <c r="S2" s="4">
+        <v>101</v>
+      </c>
+      <c r="T2" s="4">
+        <v>102</v>
+      </c>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
@@ -1206,7 +1156,7 @@
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="9">
-        <v>771</v>
+        <v>974</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1262,8 +1212,12 @@
       <c r="R3" s="4">
         <v>0</v>
       </c>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
+      <c r="S3" s="4">
+        <v>108</v>
+      </c>
+      <c r="T3" s="4">
+        <v>103</v>
+      </c>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
@@ -1277,7 +1231,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>835</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1333,8 +1287,12 @@
       <c r="R4" s="4">
         <v>25</v>
       </c>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
+      <c r="S4" s="4">
+        <v>108</v>
+      </c>
+      <c r="T4" s="4">
+        <v>0</v>
+      </c>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
@@ -1348,7 +1306,7 @@
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="9">
-        <v>684</v>
+        <v>792</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1404,8 +1362,12 @@
       <c r="R5" s="4">
         <v>23</v>
       </c>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
+      <c r="S5" s="4">
+        <v>3</v>
+      </c>
+      <c r="T5" s="4">
+        <v>111</v>
+      </c>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
@@ -1419,7 +1381,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="9">
-        <v>721</v>
+        <v>835</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1475,8 +1437,12 @@
       <c r="R6" s="4">
         <v>0</v>
       </c>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
+      <c r="S6" s="4">
+        <v>113</v>
+      </c>
+      <c r="T6" s="4">
+        <v>114</v>
+      </c>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
@@ -1490,7 +1456,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="9">
-        <v>879</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1546,8 +1512,12 @@
       <c r="R7" s="4">
         <v>0</v>
       </c>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
+      <c r="S7" s="4">
+        <v>97</v>
+      </c>
+      <c r="T7" s="4">
+        <v>65</v>
+      </c>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
@@ -1561,7 +1531,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="9">
-        <v>899</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1617,8 +1587,12 @@
       <c r="R8" s="4">
         <v>0</v>
       </c>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
+      <c r="S8" s="4">
+        <v>111</v>
+      </c>
+      <c r="T8" s="4">
+        <v>0</v>
+      </c>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
@@ -1632,7 +1606,7 @@
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="9">
-        <v>690</v>
+        <v>801</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1688,8 +1662,12 @@
       <c r="R9" s="4">
         <v>0</v>
       </c>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
+      <c r="S9" s="4">
+        <v>99</v>
+      </c>
+      <c r="T9" s="4">
+        <v>111</v>
+      </c>
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
@@ -1703,7 +1681,7 @@
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="9">
-        <v>681</v>
+        <v>891</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1759,8 +1737,12 @@
       <c r="R10" s="4">
         <v>0</v>
       </c>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
+      <c r="S10" s="4">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4">
+        <v>108</v>
+      </c>
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
@@ -1774,7 +1756,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="9">
-        <v>565</v>
+        <v>673</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1830,8 +1812,12 @@
       <c r="R11" s="4">
         <v>0</v>
       </c>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
+      <c r="S11" s="4">
+        <v>113</v>
+      </c>
+      <c r="T11" s="4">
+        <v>108</v>
+      </c>
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
@@ -1845,7 +1831,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="9">
-        <v>677</v>
+        <v>898</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -1901,8 +1887,12 @@
       <c r="R12" s="4">
         <v>0</v>
       </c>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
+      <c r="S12" s="4">
+        <v>104</v>
+      </c>
+      <c r="T12" s="4">
+        <v>20</v>
+      </c>
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
@@ -1916,7 +1906,7 @@
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="9">
-        <v>822</v>
+        <v>946</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -1972,8 +1962,12 @@
       <c r="R13" s="4">
         <v>0</v>
       </c>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
+      <c r="S13" s="4">
+        <v>113</v>
+      </c>
+      <c r="T13" s="4">
+        <v>105</v>
+      </c>
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
       <c r="W13" s="4"/>
@@ -1987,7 +1981,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>634</v>
+        <v>852</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -2043,8 +2037,12 @@
       <c r="R14" s="4">
         <v>0</v>
       </c>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
+      <c r="S14" s="4">
+        <v>111</v>
+      </c>
+      <c r="T14" s="4">
+        <v>111</v>
+      </c>
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
@@ -2058,7 +2056,7 @@
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="9">
-        <v>853</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -2114,8 +2112,12 @@
       <c r="R15" s="4">
         <v>0</v>
       </c>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
+      <c r="S15" s="4">
+        <v>66</v>
+      </c>
+      <c r="T15" s="4">
+        <v>0</v>
+      </c>
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
@@ -2129,7 +2131,7 @@
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="9">
-        <v>660</v>
+        <v>726</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -2185,8 +2187,12 @@
       <c r="R16" s="4">
         <v>0</v>
       </c>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
+      <c r="S16" s="4">
+        <v>110</v>
+      </c>
+      <c r="T16" s="4">
+        <v>109</v>
+      </c>
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
@@ -2200,7 +2206,7 @@
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="9">
-        <v>857</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -2256,8 +2262,12 @@
       <c r="R17" s="4">
         <v>0</v>
       </c>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
+      <c r="S17" s="4">
+        <v>105</v>
+      </c>
+      <c r="T17" s="4">
+        <v>106</v>
+      </c>
       <c r="U17" s="4"/>
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
@@ -2271,7 +2281,7 @@
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9">
-        <v>739</v>
+        <v>950</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -2327,8 +2337,12 @@
       <c r="R18" s="4">
         <v>0</v>
       </c>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
+      <c r="S18" s="4">
+        <v>0</v>
+      </c>
+      <c r="T18" s="4">
+        <v>108</v>
+      </c>
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
@@ -2342,7 +2356,7 @@
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
       <c r="AG18" s="9">
-        <v>746</v>
+        <v>854</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2398,8 +2412,12 @@
       <c r="R19" s="6">
         <v>79</v>
       </c>
-      <c r="S19" s="6"/>
-      <c r="T19" s="6"/>
+      <c r="S19" s="6">
+        <v>1462</v>
+      </c>
+      <c r="T19" s="6">
+        <v>1381</v>
+      </c>
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
       <c r="W19" s="6"/>
@@ -2413,7 +2431,7 @@
       <c r="AE19" s="6"/>
       <c r="AF19" s="6"/>
       <c r="AG19" s="10">
-        <v>12713</v>
+        <v>15556</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -2483,7 +2501,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.4379084967320259</v>
+        <v>2.5294117647058822</v>
       </c>
     </row>
   </sheetData>

--- a/Mei-2026.xlsx
+++ b/Mei-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5613829-736F-483E-AAF2-DDC462FB8406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BBB770-BE57-4BE1-BB62-8CC15F86C5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -565,16 +565,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="C2" s="4">
-        <v>538</v>
+        <v>612</v>
       </c>
       <c r="D2" s="9">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E2" s="13">
-        <v>3.9090909090909092</v>
+        <v>3.4615384615384617</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -584,16 +584,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c r="C3" s="4">
-        <v>740</v>
+        <v>903</v>
       </c>
       <c r="D3" s="9">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E3" s="13">
-        <v>2</v>
+        <v>2.0769230769230771</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -603,16 +603,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>346</v>
+        <v>428</v>
       </c>
       <c r="C4" s="4">
-        <v>446</v>
+        <v>577</v>
       </c>
       <c r="D4" s="9">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E4" s="13">
-        <v>3.4545454545454546</v>
+        <v>3.6153846153846154</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -622,16 +622,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>345</v>
+        <v>403</v>
       </c>
       <c r="C5" s="4">
-        <v>490</v>
+        <v>553</v>
       </c>
       <c r="D5" s="9">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E5" s="13">
-        <v>2.3636363636363638</v>
+        <v>2.4615384615384617</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -641,16 +641,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="C6" s="4">
-        <v>783</v>
+        <v>945</v>
       </c>
       <c r="D6" s="9">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E6" s="13">
-        <v>2.6363636363636362</v>
+        <v>2.6923076923076925</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -660,16 +660,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>290</v>
+        <v>358</v>
       </c>
       <c r="C7" s="4">
-        <v>771</v>
+        <v>911</v>
       </c>
       <c r="D7" s="9">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E7" s="13">
-        <v>2.0909090909090908</v>
+        <v>2.6153846153846154</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -679,16 +679,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>291</v>
+        <v>362</v>
       </c>
       <c r="C8" s="4">
-        <v>510</v>
+        <v>644</v>
       </c>
       <c r="D8" s="9">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E8" s="13">
-        <v>2.2727272727272729</v>
+        <v>2.4615384615384617</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -698,16 +698,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="C9" s="4">
-        <v>587</v>
+        <v>653</v>
       </c>
       <c r="D9" s="9">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E9" s="13">
-        <v>3.4545454545454546</v>
+        <v>3.6153846153846154</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -717,16 +717,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>258</v>
+        <v>340</v>
       </c>
       <c r="C10" s="4">
-        <v>415</v>
+        <v>548</v>
       </c>
       <c r="D10" s="9">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E10" s="13">
-        <v>3.1818181818181817</v>
+        <v>3.3846153846153846</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -736,16 +736,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>230</v>
+        <v>275</v>
       </c>
       <c r="C11" s="4">
-        <v>668</v>
+        <v>817</v>
       </c>
       <c r="D11" s="9">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E11" s="13">
-        <v>1.8181818181818181</v>
+        <v>1.8461538461538463</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -755,16 +755,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="C12" s="4">
-        <v>647</v>
+        <v>807</v>
       </c>
       <c r="D12" s="9">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E12" s="13">
-        <v>2.1818181818181817</v>
+        <v>2.0769230769230771</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -774,16 +774,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="C13" s="4">
-        <v>685</v>
+        <v>878</v>
       </c>
       <c r="D13" s="9">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E13" s="13">
-        <v>1.7272727272727273</v>
+        <v>1.8461538461538463</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -793,16 +793,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>258</v>
+        <v>325</v>
       </c>
       <c r="C14" s="4">
-        <v>817</v>
+        <v>953</v>
       </c>
       <c r="D14" s="9">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E14" s="13">
-        <v>2.4545454545454546</v>
+        <v>2.3076923076923075</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -812,16 +812,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>298</v>
+        <v>360</v>
       </c>
       <c r="C15" s="4">
-        <v>428</v>
+        <v>568</v>
       </c>
       <c r="D15" s="9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="13">
-        <v>2.2727272727272729</v>
+        <v>2</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -831,16 +831,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>268</v>
+        <v>331</v>
       </c>
       <c r="C16" s="4">
-        <v>808</v>
+        <v>970</v>
       </c>
       <c r="D16" s="9">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E16" s="13">
-        <v>2.9090909090909092</v>
+        <v>2.8461538461538463</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -850,16 +850,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>231</v>
+        <v>290</v>
       </c>
       <c r="C17" s="4">
-        <v>719</v>
+        <v>892</v>
       </c>
       <c r="D17" s="9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E17" s="13">
-        <v>1.6363636363636365</v>
+        <v>1.6153846153846154</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -869,16 +869,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="C18" s="4">
-        <v>548</v>
+        <v>625</v>
       </c>
       <c r="D18" s="9">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E18" s="13">
-        <v>2.6363636363636362</v>
+        <v>2.7692307692307692</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -888,16 +888,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>4956</v>
+        <v>5923</v>
       </c>
       <c r="C19" s="6">
-        <v>10600</v>
+        <v>12856</v>
       </c>
       <c r="D19" s="10">
-        <v>473</v>
+        <v>568</v>
       </c>
       <c r="E19" s="14">
-        <v>2.5294117647058822</v>
+        <v>2.570135746606335</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1143,8 +1143,12 @@
       <c r="T2" s="4">
         <v>102</v>
       </c>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
+      <c r="U2" s="4">
+        <v>0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>106</v>
+      </c>
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
@@ -1156,7 +1160,7 @@
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="9">
-        <v>974</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1218,8 +1222,12 @@
       <c r="T3" s="4">
         <v>103</v>
       </c>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
+      <c r="U3" s="4">
+        <v>106</v>
+      </c>
+      <c r="V3" s="4">
+        <v>104</v>
+      </c>
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
@@ -1231,7 +1239,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>1046</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1293,8 +1301,12 @@
       <c r="T4" s="4">
         <v>0</v>
       </c>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
+      <c r="U4" s="4">
+        <v>103</v>
+      </c>
+      <c r="V4" s="4">
+        <v>110</v>
+      </c>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
@@ -1306,7 +1318,7 @@
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="9">
-        <v>792</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1368,8 +1380,12 @@
       <c r="T5" s="4">
         <v>111</v>
       </c>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
+      <c r="U5" s="4">
+        <v>0</v>
+      </c>
+      <c r="V5" s="4">
+        <v>121</v>
+      </c>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
@@ -1381,7 +1397,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="9">
-        <v>835</v>
+        <v>956</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1443,8 +1459,12 @@
       <c r="T6" s="4">
         <v>114</v>
       </c>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
+      <c r="U6" s="4">
+        <v>108</v>
+      </c>
+      <c r="V6" s="4">
+        <v>119</v>
+      </c>
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
@@ -1456,7 +1476,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="9">
-        <v>1106</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1518,8 +1538,12 @@
       <c r="T7" s="4">
         <v>65</v>
       </c>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
+      <c r="U7" s="4">
+        <v>100</v>
+      </c>
+      <c r="V7" s="4">
+        <v>108</v>
+      </c>
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
@@ -1531,7 +1555,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="9">
-        <v>1061</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1593,8 +1617,12 @@
       <c r="T8" s="4">
         <v>0</v>
       </c>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
+      <c r="U8" s="4">
+        <v>96</v>
+      </c>
+      <c r="V8" s="4">
+        <v>109</v>
+      </c>
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
@@ -1606,7 +1634,7 @@
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="9">
-        <v>801</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1668,8 +1696,12 @@
       <c r="T9" s="4">
         <v>111</v>
       </c>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
+      <c r="U9" s="4">
+        <v>0</v>
+      </c>
+      <c r="V9" s="4">
+        <v>104</v>
+      </c>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
@@ -1681,7 +1713,7 @@
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="9">
-        <v>891</v>
+        <v>995</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1743,8 +1775,12 @@
       <c r="T10" s="4">
         <v>108</v>
       </c>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
+      <c r="U10" s="4">
+        <v>108</v>
+      </c>
+      <c r="V10" s="4">
+        <v>107</v>
+      </c>
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
@@ -1756,7 +1792,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="9">
-        <v>673</v>
+        <v>888</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1818,8 +1854,12 @@
       <c r="T11" s="4">
         <v>108</v>
       </c>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
+      <c r="U11" s="4">
+        <v>88</v>
+      </c>
+      <c r="V11" s="4">
+        <v>106</v>
+      </c>
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
@@ -1831,7 +1871,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="9">
-        <v>898</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -1893,8 +1933,12 @@
       <c r="T12" s="4">
         <v>20</v>
       </c>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
+      <c r="U12" s="4">
+        <v>109</v>
+      </c>
+      <c r="V12" s="4">
+        <v>111</v>
+      </c>
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
@@ -1906,7 +1950,7 @@
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="9">
-        <v>946</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -1968,8 +2012,12 @@
       <c r="T13" s="4">
         <v>105</v>
       </c>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
+      <c r="U13" s="4">
+        <v>124</v>
+      </c>
+      <c r="V13" s="4">
+        <v>104</v>
+      </c>
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
@@ -1981,7 +2029,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>852</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -2043,8 +2091,12 @@
       <c r="T14" s="4">
         <v>111</v>
       </c>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
+      <c r="U14" s="4">
+        <v>99</v>
+      </c>
+      <c r="V14" s="4">
+        <v>104</v>
+      </c>
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
@@ -2056,7 +2108,7 @@
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="9">
-        <v>1075</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -2118,8 +2170,12 @@
       <c r="T15" s="4">
         <v>0</v>
       </c>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
+      <c r="U15" s="4">
+        <v>68</v>
+      </c>
+      <c r="V15" s="4">
+        <v>134</v>
+      </c>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
@@ -2131,7 +2187,7 @@
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="9">
-        <v>726</v>
+        <v>928</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -2193,8 +2249,12 @@
       <c r="T16" s="4">
         <v>109</v>
       </c>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
+      <c r="U16" s="4">
+        <v>111</v>
+      </c>
+      <c r="V16" s="4">
+        <v>114</v>
+      </c>
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
@@ -2206,7 +2266,7 @@
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="9">
-        <v>1076</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -2268,8 +2328,12 @@
       <c r="T17" s="4">
         <v>106</v>
       </c>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
+      <c r="U17" s="4">
+        <v>106</v>
+      </c>
+      <c r="V17" s="4">
+        <v>126</v>
+      </c>
       <c r="W17" s="4"/>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
@@ -2281,7 +2345,7 @@
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9">
-        <v>950</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -2343,8 +2407,12 @@
       <c r="T18" s="4">
         <v>108</v>
       </c>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
+      <c r="U18" s="4">
+        <v>110</v>
+      </c>
+      <c r="V18" s="4">
+        <v>0</v>
+      </c>
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
@@ -2356,7 +2424,7 @@
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
       <c r="AG18" s="9">
-        <v>854</v>
+        <v>964</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2418,8 +2486,12 @@
       <c r="T19" s="6">
         <v>1381</v>
       </c>
-      <c r="U19" s="6"/>
-      <c r="V19" s="6"/>
+      <c r="U19" s="6">
+        <v>1436</v>
+      </c>
+      <c r="V19" s="6">
+        <v>1787</v>
+      </c>
       <c r="W19" s="6"/>
       <c r="X19" s="6"/>
       <c r="Y19" s="6"/>
@@ -2431,7 +2503,7 @@
       <c r="AE19" s="6"/>
       <c r="AF19" s="6"/>
       <c r="AG19" s="10">
-        <v>15556</v>
+        <v>18779</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -2501,7 +2573,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.5294117647058822</v>
+        <v>2.570135746606335</v>
       </c>
     </row>
   </sheetData>

--- a/Mei-2026.xlsx
+++ b/Mei-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BBB770-BE57-4BE1-BB62-8CC15F86C5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837769E3-6712-4214-85F9-5C0D4CE210F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -574,7 +574,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="13">
-        <v>3.4615384615384617</v>
+        <v>3.5714285714285716</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -593,7 +593,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="13">
-        <v>2.0769230769230771</v>
+        <v>2.4285714285714284</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -612,7 +612,7 @@
         <v>47</v>
       </c>
       <c r="E4" s="13">
-        <v>3.6153846153846154</v>
+        <v>4.1428571428571432</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -631,7 +631,7 @@
         <v>32</v>
       </c>
       <c r="E5" s="13">
-        <v>2.4615384615384617</v>
+        <v>2.5714285714285716</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -650,7 +650,7 @@
         <v>35</v>
       </c>
       <c r="E6" s="13">
-        <v>2.6923076923076925</v>
+        <v>2.7857142857142856</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -669,7 +669,7 @@
         <v>34</v>
       </c>
       <c r="E7" s="13">
-        <v>2.6153846153846154</v>
+        <v>2.7142857142857144</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -688,7 +688,7 @@
         <v>32</v>
       </c>
       <c r="E8" s="13">
-        <v>2.4615384615384617</v>
+        <v>2.6428571428571428</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -707,7 +707,7 @@
         <v>47</v>
       </c>
       <c r="E9" s="13">
-        <v>3.6153846153846154</v>
+        <v>3.7142857142857144</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -726,7 +726,7 @@
         <v>44</v>
       </c>
       <c r="E10" s="13">
-        <v>3.3846153846153846</v>
+        <v>4.1428571428571432</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -745,7 +745,7 @@
         <v>24</v>
       </c>
       <c r="E11" s="13">
-        <v>1.8461538461538463</v>
+        <v>2.2142857142857144</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -764,7 +764,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="13">
-        <v>2.0769230769230771</v>
+        <v>2.0714285714285716</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -783,7 +783,7 @@
         <v>24</v>
       </c>
       <c r="E13" s="13">
-        <v>1.8461538461538463</v>
+        <v>2.1428571428571428</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -802,7 +802,7 @@
         <v>30</v>
       </c>
       <c r="E14" s="13">
-        <v>2.3076923076923075</v>
+        <v>2.7142857142857144</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -840,7 +840,7 @@
         <v>37</v>
       </c>
       <c r="E16" s="13">
-        <v>2.8461538461538463</v>
+        <v>3.0714285714285716</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -859,7 +859,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="13">
-        <v>1.6153846153846154</v>
+        <v>2</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -878,7 +878,7 @@
         <v>36</v>
       </c>
       <c r="E18" s="13">
-        <v>2.7692307692307692</v>
+        <v>3</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -897,7 +897,7 @@
         <v>568</v>
       </c>
       <c r="E19" s="14">
-        <v>2.570135746606335</v>
+        <v>2.8193277310924372</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1149,9 +1149,15 @@
       <c r="V2" s="4">
         <v>106</v>
       </c>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
+      <c r="W2" s="4">
+        <v>121</v>
+      </c>
+      <c r="X2" s="4">
+        <v>60</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>0</v>
+      </c>
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
@@ -1160,7 +1166,7 @@
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="9">
-        <v>1080</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1228,9 +1234,15 @@
       <c r="V3" s="4">
         <v>104</v>
       </c>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
+      <c r="W3" s="4">
+        <v>106</v>
+      </c>
+      <c r="X3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>0</v>
+      </c>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
       <c r="AB3" s="4"/>
@@ -1239,7 +1251,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>1256</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1307,9 +1319,15 @@
       <c r="V4" s="4">
         <v>110</v>
       </c>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
+      <c r="W4" s="4">
+        <v>139</v>
+      </c>
+      <c r="X4" s="4">
+        <v>58</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>9</v>
+      </c>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
       <c r="AB4" s="4"/>
@@ -1318,7 +1336,7 @@
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="9">
-        <v>1005</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1386,9 +1404,15 @@
       <c r="V5" s="4">
         <v>121</v>
       </c>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
+      <c r="W5" s="4">
+        <v>0</v>
+      </c>
+      <c r="X5" s="4">
+        <v>81</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>0</v>
+      </c>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
       <c r="AB5" s="4"/>
@@ -1397,7 +1421,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="9">
-        <v>956</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1465,9 +1489,15 @@
       <c r="V6" s="4">
         <v>119</v>
       </c>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
+      <c r="W6" s="4">
+        <v>138</v>
+      </c>
+      <c r="X6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>0</v>
+      </c>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
       <c r="AB6" s="4"/>
@@ -1476,7 +1506,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="9">
-        <v>1333</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1544,9 +1574,15 @@
       <c r="V7" s="4">
         <v>108</v>
       </c>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
+      <c r="W7" s="4">
+        <v>127</v>
+      </c>
+      <c r="X7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="4">
+        <v>0</v>
+      </c>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4"/>
       <c r="AB7" s="4"/>
@@ -1555,7 +1591,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="9">
-        <v>1269</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1623,9 +1659,15 @@
       <c r="V8" s="4">
         <v>109</v>
       </c>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
+      <c r="W8" s="4">
+        <v>121</v>
+      </c>
+      <c r="X8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>0</v>
+      </c>
       <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
@@ -1634,7 +1676,7 @@
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="9">
-        <v>1006</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1702,9 +1744,15 @@
       <c r="V9" s="4">
         <v>104</v>
       </c>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
+      <c r="W9" s="4">
+        <v>152</v>
+      </c>
+      <c r="X9" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>0</v>
+      </c>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
       <c r="AB9" s="4"/>
@@ -1713,7 +1761,7 @@
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="9">
-        <v>995</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1781,9 +1829,15 @@
       <c r="V10" s="4">
         <v>107</v>
       </c>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
+      <c r="W10" s="4">
+        <v>131</v>
+      </c>
+      <c r="X10" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>42</v>
+      </c>
       <c r="Z10" s="4"/>
       <c r="AA10" s="4"/>
       <c r="AB10" s="4"/>
@@ -1792,7 +1846,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="9">
-        <v>888</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1860,9 +1914,15 @@
       <c r="V11" s="4">
         <v>106</v>
       </c>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
+      <c r="W11" s="4">
+        <v>134</v>
+      </c>
+      <c r="X11" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>0</v>
+      </c>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
       <c r="AB11" s="4"/>
@@ -1871,7 +1931,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="9">
-        <v>1092</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -1939,9 +1999,15 @@
       <c r="V12" s="4">
         <v>111</v>
       </c>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
+      <c r="W12" s="4">
+        <v>0</v>
+      </c>
+      <c r="X12" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>0</v>
+      </c>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
       <c r="AB12" s="4"/>
@@ -2018,9 +2084,15 @@
       <c r="V13" s="4">
         <v>104</v>
       </c>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
+      <c r="W13" s="4">
+        <v>135</v>
+      </c>
+      <c r="X13" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>0</v>
+      </c>
       <c r="Z13" s="4"/>
       <c r="AA13" s="4"/>
       <c r="AB13" s="4"/>
@@ -2029,7 +2101,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>1080</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -2097,9 +2169,15 @@
       <c r="V14" s="4">
         <v>104</v>
       </c>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
+      <c r="W14" s="4">
+        <v>137</v>
+      </c>
+      <c r="X14" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="4">
+        <v>0</v>
+      </c>
       <c r="Z14" s="4"/>
       <c r="AA14" s="4"/>
       <c r="AB14" s="4"/>
@@ -2108,7 +2186,7 @@
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="9">
-        <v>1278</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -2176,9 +2254,15 @@
       <c r="V15" s="4">
         <v>134</v>
       </c>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="4"/>
+      <c r="W15" s="4">
+        <v>0</v>
+      </c>
+      <c r="X15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>77</v>
+      </c>
       <c r="Z15" s="4"/>
       <c r="AA15" s="4"/>
       <c r="AB15" s="4"/>
@@ -2187,7 +2271,7 @@
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="9">
-        <v>928</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -2255,9 +2339,15 @@
       <c r="V16" s="4">
         <v>114</v>
       </c>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
+      <c r="W16" s="4">
+        <v>156</v>
+      </c>
+      <c r="X16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="4">
+        <v>0</v>
+      </c>
       <c r="Z16" s="4"/>
       <c r="AA16" s="4"/>
       <c r="AB16" s="4"/>
@@ -2266,7 +2356,7 @@
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="9">
-        <v>1301</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -2334,9 +2424,15 @@
       <c r="V17" s="4">
         <v>126</v>
       </c>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
+      <c r="W17" s="4">
+        <v>153</v>
+      </c>
+      <c r="X17" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="4">
+        <v>0</v>
+      </c>
       <c r="Z17" s="4"/>
       <c r="AA17" s="4"/>
       <c r="AB17" s="4"/>
@@ -2345,7 +2441,7 @@
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9">
-        <v>1182</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -2413,9 +2509,15 @@
       <c r="V18" s="4">
         <v>0</v>
       </c>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
+      <c r="W18" s="4">
+        <v>135</v>
+      </c>
+      <c r="X18" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="4">
+        <v>68</v>
+      </c>
       <c r="Z18" s="4"/>
       <c r="AA18" s="4"/>
       <c r="AB18" s="4"/>
@@ -2424,7 +2526,7 @@
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
       <c r="AG18" s="9">
-        <v>964</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2492,9 +2594,15 @@
       <c r="V19" s="6">
         <v>1787</v>
       </c>
-      <c r="W19" s="6"/>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="6"/>
+      <c r="W19" s="6">
+        <v>1885</v>
+      </c>
+      <c r="X19" s="6">
+        <v>199</v>
+      </c>
+      <c r="Y19" s="6">
+        <v>196</v>
+      </c>
       <c r="Z19" s="6"/>
       <c r="AA19" s="6"/>
       <c r="AB19" s="6"/>
@@ -2503,7 +2611,7 @@
       <c r="AE19" s="6"/>
       <c r="AF19" s="6"/>
       <c r="AG19" s="10">
-        <v>18779</v>
+        <v>21059</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -2573,7 +2681,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.570135746606335</v>
+        <v>2.8193277310924372</v>
       </c>
     </row>
   </sheetData>

--- a/Mei-2026.xlsx
+++ b/Mei-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837769E3-6712-4214-85F9-5C0D4CE210F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E389C57-4F33-44AA-B187-A4B6492905F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -565,13 +565,13 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>468</v>
+        <v>572</v>
       </c>
       <c r="C2" s="4">
-        <v>612</v>
+        <v>689</v>
       </c>
       <c r="D2" s="9">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E2" s="13">
         <v>3.5714285714285716</v>
@@ -584,13 +584,13 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="C3" s="4">
-        <v>903</v>
+        <v>970</v>
       </c>
       <c r="D3" s="9">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E3" s="13">
         <v>2.4285714285714284</v>
@@ -603,13 +603,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>428</v>
+        <v>543</v>
       </c>
       <c r="C4" s="4">
-        <v>577</v>
+        <v>668</v>
       </c>
       <c r="D4" s="9">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E4" s="13">
         <v>4.1428571428571432</v>
@@ -622,13 +622,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>403</v>
+        <v>470</v>
       </c>
       <c r="C5" s="4">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="D5" s="9">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E5" s="13">
         <v>2.5714285714285716</v>
@@ -641,13 +641,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>388</v>
+        <v>442</v>
       </c>
       <c r="C6" s="4">
-        <v>945</v>
+        <v>1029</v>
       </c>
       <c r="D6" s="9">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E6" s="13">
         <v>2.7857142857142856</v>
@@ -660,13 +660,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>358</v>
+        <v>398</v>
       </c>
       <c r="C7" s="4">
-        <v>911</v>
+        <v>998</v>
       </c>
       <c r="D7" s="9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7" s="13">
         <v>2.7142857142857144</v>
@@ -679,13 +679,13 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>362</v>
+        <v>402</v>
       </c>
       <c r="C8" s="4">
-        <v>644</v>
+        <v>725</v>
       </c>
       <c r="D8" s="9">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E8" s="13">
         <v>2.6428571428571428</v>
@@ -698,13 +698,13 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>342</v>
+        <v>406</v>
       </c>
       <c r="C9" s="4">
-        <v>653</v>
+        <v>741</v>
       </c>
       <c r="D9" s="9">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E9" s="13">
         <v>3.7142857142857144</v>
@@ -717,13 +717,13 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>340</v>
+        <v>440</v>
       </c>
       <c r="C10" s="4">
-        <v>548</v>
+        <v>621</v>
       </c>
       <c r="D10" s="9">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E10" s="13">
         <v>4.1428571428571432</v>
@@ -736,13 +736,13 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>275</v>
+        <v>338</v>
       </c>
       <c r="C11" s="4">
-        <v>817</v>
+        <v>888</v>
       </c>
       <c r="D11" s="9">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E11" s="13">
         <v>2.2142857142857144</v>
@@ -761,7 +761,7 @@
         <v>807</v>
       </c>
       <c r="D12" s="9">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E12" s="13">
         <v>2.0714285714285716</v>
@@ -774,13 +774,13 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>202</v>
+        <v>240</v>
       </c>
       <c r="C13" s="4">
-        <v>878</v>
+        <v>975</v>
       </c>
       <c r="D13" s="9">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E13" s="13">
         <v>2.1428571428571428</v>
@@ -793,13 +793,13 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>325</v>
+        <v>376</v>
       </c>
       <c r="C14" s="4">
-        <v>953</v>
+        <v>1039</v>
       </c>
       <c r="D14" s="9">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E14" s="13">
         <v>2.7142857142857144</v>
@@ -812,13 +812,13 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>360</v>
+        <v>437</v>
       </c>
       <c r="C15" s="4">
         <v>568</v>
       </c>
       <c r="D15" s="9">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E15" s="13">
         <v>2</v>
@@ -831,13 +831,13 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>331</v>
+        <v>399</v>
       </c>
       <c r="C16" s="4">
-        <v>970</v>
+        <v>1058</v>
       </c>
       <c r="D16" s="9">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E16" s="13">
         <v>3.0714285714285716</v>
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>290</v>
+        <v>344</v>
       </c>
       <c r="C17" s="4">
-        <v>892</v>
+        <v>991</v>
       </c>
       <c r="D17" s="9">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E17" s="13">
         <v>2</v>
@@ -869,13 +869,13 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>339</v>
+        <v>446</v>
       </c>
       <c r="C18" s="4">
-        <v>625</v>
+        <v>721</v>
       </c>
       <c r="D18" s="9">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E18" s="13">
         <v>3</v>
@@ -888,13 +888,13 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>5923</v>
+        <v>7004</v>
       </c>
       <c r="C19" s="6">
-        <v>12856</v>
+        <v>14055</v>
       </c>
       <c r="D19" s="10">
-        <v>568</v>
+        <v>671</v>
       </c>
       <c r="E19" s="14">
         <v>2.8193277310924372</v>

--- a/Mei-2026.xlsx
+++ b/Mei-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E389C57-4F33-44AA-B187-A4B6492905F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57230CCA-BA3C-47BF-94F4-98A5089EB545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -565,16 +565,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>572</v>
+        <v>591</v>
       </c>
       <c r="C2" s="4">
-        <v>689</v>
+        <v>760</v>
       </c>
       <c r="D2" s="9">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E2" s="13">
-        <v>3.5714285714285716</v>
+        <v>3.3125</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -584,16 +584,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>392</v>
+        <v>443</v>
       </c>
       <c r="C3" s="4">
-        <v>970</v>
+        <v>1144</v>
       </c>
       <c r="D3" s="9">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E3" s="13">
-        <v>2.4285714285714284</v>
+        <v>2.5625</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -603,16 +603,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>543</v>
+        <v>579</v>
       </c>
       <c r="C4" s="4">
-        <v>668</v>
+        <v>742</v>
       </c>
       <c r="D4" s="9">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E4" s="13">
-        <v>4.1428571428571432</v>
+        <v>3.8125</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -622,16 +622,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>470</v>
+        <v>552</v>
       </c>
       <c r="C5" s="4">
-        <v>567</v>
+        <v>696</v>
       </c>
       <c r="D5" s="9">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E5" s="13">
-        <v>2.5714285714285716</v>
+        <v>3</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -641,16 +641,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>442</v>
+        <v>501</v>
       </c>
       <c r="C6" s="4">
-        <v>1029</v>
+        <v>1197</v>
       </c>
       <c r="D6" s="9">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E6" s="13">
-        <v>2.7857142857142856</v>
+        <v>2.6875</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -660,16 +660,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>398</v>
+        <v>460</v>
       </c>
       <c r="C7" s="4">
-        <v>998</v>
+        <v>1179</v>
       </c>
       <c r="D7" s="9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7" s="13">
-        <v>2.7142857142857144</v>
+        <v>2.5</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -679,16 +679,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>402</v>
+        <v>481</v>
       </c>
       <c r="C8" s="4">
-        <v>725</v>
+        <v>868</v>
       </c>
       <c r="D8" s="9">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E8" s="13">
-        <v>2.6428571428571428</v>
+        <v>3.0625</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -698,16 +698,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>406</v>
+        <v>467</v>
       </c>
       <c r="C9" s="4">
-        <v>741</v>
+        <v>908</v>
       </c>
       <c r="D9" s="9">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E9" s="13">
-        <v>3.7142857142857144</v>
+        <v>3.625</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -717,16 +717,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>440</v>
+        <v>481</v>
       </c>
       <c r="C10" s="4">
-        <v>621</v>
+        <v>685</v>
       </c>
       <c r="D10" s="9">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="E10" s="13">
-        <v>4.1428571428571432</v>
+        <v>4.625</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -736,16 +736,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>338</v>
+        <v>380</v>
       </c>
       <c r="C11" s="4">
-        <v>888</v>
+        <v>1066</v>
       </c>
       <c r="D11" s="9">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E11" s="13">
-        <v>2.2142857142857144</v>
+        <v>2.375</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -755,16 +755,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>359</v>
+        <v>420</v>
       </c>
       <c r="C12" s="4">
-        <v>807</v>
+        <v>969</v>
       </c>
       <c r="D12" s="9">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E12" s="13">
-        <v>2.0714285714285716</v>
+        <v>1.9375</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -774,16 +774,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="C13" s="4">
-        <v>975</v>
+        <v>1080</v>
       </c>
       <c r="D13" s="9">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E13" s="13">
-        <v>2.1428571428571428</v>
+        <v>2.25</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -793,16 +793,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="C14" s="4">
-        <v>1039</v>
+        <v>1181</v>
       </c>
       <c r="D14" s="9">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E14" s="13">
-        <v>2.7142857142857144</v>
+        <v>2.75</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -812,16 +812,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="C15" s="4">
-        <v>568</v>
+        <v>662</v>
       </c>
       <c r="D15" s="9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E15" s="13">
-        <v>2</v>
+        <v>1.8125</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -831,16 +831,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>399</v>
+        <v>457</v>
       </c>
       <c r="C16" s="4">
-        <v>1058</v>
+        <v>1226</v>
       </c>
       <c r="D16" s="9">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E16" s="13">
-        <v>3.0714285714285716</v>
+        <v>3.1875</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>344</v>
+        <v>397</v>
       </c>
       <c r="C17" s="4">
-        <v>991</v>
+        <v>1154</v>
       </c>
       <c r="D17" s="9">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E17" s="13">
         <v>2</v>
@@ -869,16 +869,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="C18" s="4">
-        <v>721</v>
+        <v>804</v>
       </c>
       <c r="D18" s="9">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E18" s="13">
-        <v>3</v>
+        <v>2.9375</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -888,16 +888,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>7004</v>
+        <v>7829</v>
       </c>
       <c r="C19" s="6">
-        <v>14055</v>
+        <v>16321</v>
       </c>
       <c r="D19" s="10">
-        <v>671</v>
+        <v>775</v>
       </c>
       <c r="E19" s="14">
-        <v>2.8193277310924372</v>
+        <v>2.8492647058823528</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -1158,15 +1158,19 @@
       <c r="Y2" s="4">
         <v>0</v>
       </c>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
+      <c r="Z2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>90</v>
+      </c>
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="9">
-        <v>1261</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1243,15 +1247,19 @@
       <c r="Y3" s="4">
         <v>0</v>
       </c>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
+      <c r="Z3" s="4">
+        <v>114</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>111</v>
+      </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>1362</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1328,15 +1336,19 @@
       <c r="Y4" s="4">
         <v>9</v>
       </c>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
+      <c r="Z4" s="4">
+        <v>110</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>0</v>
+      </c>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="9">
-        <v>1211</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1413,15 +1425,19 @@
       <c r="Y5" s="4">
         <v>0</v>
       </c>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
+      <c r="Z5" s="4">
+        <v>108</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>103</v>
+      </c>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="9">
-        <v>1037</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1498,15 +1514,19 @@
       <c r="Y6" s="4">
         <v>0</v>
       </c>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
+      <c r="Z6" s="4">
+        <v>117</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>110</v>
+      </c>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="9">
-        <v>1471</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1583,15 +1603,19 @@
       <c r="Y7" s="4">
         <v>0</v>
       </c>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="4"/>
+      <c r="Z7" s="4">
+        <v>127</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>116</v>
+      </c>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="9">
-        <v>1396</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1668,15 +1692,19 @@
       <c r="Y8" s="4">
         <v>0</v>
       </c>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
+      <c r="Z8" s="4">
+        <v>112</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>110</v>
+      </c>
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="9">
-        <v>1127</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1753,15 +1781,19 @@
       <c r="Y9" s="4">
         <v>0</v>
       </c>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="4"/>
+      <c r="Z9" s="4">
+        <v>118</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>110</v>
+      </c>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="9">
-        <v>1147</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1838,15 +1870,19 @@
       <c r="Y10" s="4">
         <v>42</v>
       </c>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="4"/>
+      <c r="Z10" s="4">
+        <v>105</v>
+      </c>
+      <c r="AA10" s="4">
+        <v>0</v>
+      </c>
       <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="9">
-        <v>1061</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1923,15 +1959,19 @@
       <c r="Y11" s="4">
         <v>0</v>
       </c>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4"/>
+      <c r="Z11" s="4">
+        <v>113</v>
+      </c>
+      <c r="AA11" s="4">
+        <v>107</v>
+      </c>
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="9">
-        <v>1226</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -2008,15 +2048,19 @@
       <c r="Y12" s="4">
         <v>0</v>
       </c>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
+      <c r="Z12" s="4">
+        <v>119</v>
+      </c>
+      <c r="AA12" s="4">
+        <v>104</v>
+      </c>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="9">
-        <v>1166</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -2093,15 +2137,19 @@
       <c r="Y13" s="4">
         <v>0</v>
       </c>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="4"/>
+      <c r="Z13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="4">
+        <v>129</v>
+      </c>
       <c r="AB13" s="4"/>
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>1215</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -2178,15 +2226,19 @@
       <c r="Y14" s="4">
         <v>0</v>
       </c>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
+      <c r="Z14" s="4">
+        <v>97</v>
+      </c>
+      <c r="AA14" s="4">
+        <v>90</v>
+      </c>
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="9">
-        <v>1415</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -2263,15 +2315,19 @@
       <c r="Y15" s="4">
         <v>77</v>
       </c>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="4"/>
+      <c r="Z15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="4">
+        <v>121</v>
+      </c>
       <c r="AB15" s="4"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="9">
-        <v>1005</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -2348,15 +2404,19 @@
       <c r="Y16" s="4">
         <v>0</v>
       </c>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="4"/>
+      <c r="Z16" s="4">
+        <v>111</v>
+      </c>
+      <c r="AA16" s="4">
+        <v>115</v>
+      </c>
       <c r="AB16" s="4"/>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="9">
-        <v>1457</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -2433,15 +2493,19 @@
       <c r="Y17" s="4">
         <v>0</v>
       </c>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="4"/>
+      <c r="Z17" s="4">
+        <v>114</v>
+      </c>
+      <c r="AA17" s="4">
+        <v>102</v>
+      </c>
       <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9">
-        <v>1335</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -2518,15 +2582,19 @@
       <c r="Y18" s="4">
         <v>68</v>
       </c>
-      <c r="Z18" s="4"/>
-      <c r="AA18" s="4"/>
+      <c r="Z18" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="4">
+        <v>107</v>
+      </c>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
       <c r="AG18" s="9">
-        <v>1167</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2603,15 +2671,19 @@
       <c r="Y19" s="6">
         <v>196</v>
       </c>
-      <c r="Z19" s="6"/>
-      <c r="AA19" s="6"/>
+      <c r="Z19" s="6">
+        <v>1466</v>
+      </c>
+      <c r="AA19" s="6">
+        <v>1625</v>
+      </c>
       <c r="AB19" s="6"/>
       <c r="AC19" s="6"/>
       <c r="AD19" s="6"/>
       <c r="AE19" s="6"/>
       <c r="AF19" s="6"/>
       <c r="AG19" s="10">
-        <v>21059</v>
+        <v>24150</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -2681,7 +2753,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.8193277310924372</v>
+        <v>2.8492647058823528</v>
       </c>
     </row>
   </sheetData>

--- a/Mei-2026.xlsx
+++ b/Mei-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57230CCA-BA3C-47BF-94F4-98A5089EB545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF58B2B-7658-4CEC-8E0C-166C1422E8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -540,7 +540,11 @@
   <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="21.5703125" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -565,16 +569,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C2" s="4">
-        <v>760</v>
+        <v>905</v>
       </c>
       <c r="D2" s="9">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E2" s="13">
-        <v>3.3125</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -584,16 +588,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="C3" s="4">
         <v>1144</v>
       </c>
       <c r="D3" s="9">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E3" s="13">
-        <v>2.5625</v>
+        <v>2.5</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -603,16 +607,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>579</v>
+        <v>611</v>
       </c>
       <c r="C4" s="4">
-        <v>742</v>
+        <v>869</v>
       </c>
       <c r="D4" s="9">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E4" s="13">
-        <v>3.8125</v>
+        <v>3.8888888888888888</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -622,16 +626,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>552</v>
+        <v>597</v>
       </c>
       <c r="C5" s="4">
-        <v>696</v>
+        <v>808</v>
       </c>
       <c r="D5" s="9">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E5" s="13">
-        <v>3</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -641,16 +645,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>501</v>
+        <v>544</v>
       </c>
       <c r="C6" s="4">
-        <v>1197</v>
+        <v>1358</v>
       </c>
       <c r="D6" s="9">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E6" s="13">
-        <v>2.6875</v>
+        <v>2.7222222222222223</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -660,16 +664,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>460</v>
+        <v>509</v>
       </c>
       <c r="C7" s="4">
-        <v>1179</v>
+        <v>1308</v>
       </c>
       <c r="D7" s="9">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E7" s="13">
-        <v>2.5</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -679,16 +683,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>481</v>
+        <v>536</v>
       </c>
       <c r="C8" s="4">
-        <v>868</v>
+        <v>1013</v>
       </c>
       <c r="D8" s="9">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E8" s="13">
-        <v>3.0625</v>
+        <v>3.2222222222222223</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -698,16 +702,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>467</v>
+        <v>512</v>
       </c>
       <c r="C9" s="4">
-        <v>908</v>
+        <v>1033</v>
       </c>
       <c r="D9" s="9">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E9" s="13">
-        <v>3.625</v>
+        <v>4.4444444444444446</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -717,16 +721,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C10" s="4">
-        <v>685</v>
+        <v>759</v>
       </c>
       <c r="D10" s="9">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E10" s="13">
-        <v>4.625</v>
+        <v>4.4444444444444446</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -736,16 +740,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C11" s="4">
-        <v>1066</v>
+        <v>1225</v>
       </c>
       <c r="D11" s="9">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E11" s="13">
-        <v>2.375</v>
+        <v>2.5555555555555554</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -755,16 +759,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>420</v>
+        <v>484</v>
       </c>
       <c r="C12" s="4">
-        <v>969</v>
+        <v>1141</v>
       </c>
       <c r="D12" s="9">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E12" s="13">
-        <v>1.9375</v>
+        <v>2.1666666666666665</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -774,16 +778,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="C13" s="4">
-        <v>1080</v>
+        <v>1246</v>
       </c>
       <c r="D13" s="9">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E13" s="13">
-        <v>2.25</v>
+        <v>2.5555555555555554</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -793,16 +797,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>421</v>
+        <v>452</v>
       </c>
       <c r="C14" s="4">
-        <v>1181</v>
+        <v>1318</v>
       </c>
       <c r="D14" s="9">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E14" s="13">
-        <v>2.75</v>
+        <v>2.7222222222222223</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -812,16 +816,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>464</v>
+        <v>486</v>
       </c>
       <c r="C15" s="4">
-        <v>662</v>
+        <v>772</v>
       </c>
       <c r="D15" s="9">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E15" s="13">
-        <v>1.8125</v>
+        <v>1.9444444444444444</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -831,16 +835,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="C16" s="4">
-        <v>1226</v>
+        <v>1343</v>
       </c>
       <c r="D16" s="9">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E16" s="13">
-        <v>3.1875</v>
+        <v>3.2222222222222223</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -850,16 +854,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C17" s="4">
-        <v>1154</v>
+        <v>1326</v>
       </c>
       <c r="D17" s="9">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E17" s="13">
-        <v>2</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -869,16 +873,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="4">
-        <v>471</v>
+        <v>499</v>
       </c>
       <c r="C18" s="4">
-        <v>804</v>
+        <v>970</v>
       </c>
       <c r="D18" s="9">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E18" s="13">
-        <v>2.9375</v>
+        <v>3.4444444444444446</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -888,16 +892,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="6">
-        <v>7829</v>
+        <v>8261</v>
       </c>
       <c r="C19" s="6">
-        <v>16321</v>
+        <v>18538</v>
       </c>
       <c r="D19" s="10">
-        <v>775</v>
+        <v>951</v>
       </c>
       <c r="E19" s="14">
-        <v>2.8492647058823528</v>
+        <v>3.107843137254902</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -979,8 +983,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="32" width="7.28515625" customWidth="1"/>
-    <col min="33" max="33" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="32" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.25">
@@ -1127,7 +1134,9 @@
       <c r="N2" s="4">
         <v>76</v>
       </c>
-      <c r="O2" s="4"/>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
       <c r="P2" s="4">
         <v>103</v>
       </c>
@@ -1150,10 +1159,10 @@
         <v>106</v>
       </c>
       <c r="W2" s="4">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="X2" s="4">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="Y2" s="4">
         <v>0</v>
@@ -1164,13 +1173,23 @@
       <c r="AA2" s="4">
         <v>90</v>
       </c>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
+      <c r="AB2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>91</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>105</v>
+      </c>
+      <c r="AE2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="4">
+        <v>0</v>
+      </c>
       <c r="AG2" s="9">
-        <v>1351</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1216,7 +1235,9 @@
       <c r="N3" s="4">
         <v>93</v>
       </c>
-      <c r="O3" s="4"/>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
       <c r="P3" s="4">
         <v>85</v>
       </c>
@@ -1239,7 +1260,7 @@
         <v>104</v>
       </c>
       <c r="W3" s="4">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="X3" s="4">
         <v>0</v>
@@ -1253,13 +1274,23 @@
       <c r="AA3" s="4">
         <v>111</v>
       </c>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="4"/>
-      <c r="AD3" s="4"/>
-      <c r="AE3" s="4"/>
-      <c r="AF3" s="4"/>
+      <c r="AB3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="4">
+        <v>5</v>
+      </c>
+      <c r="AE3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="4">
+        <v>0</v>
+      </c>
       <c r="AG3" s="9">
-        <v>1587</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1305,7 +1336,9 @@
       <c r="N4" s="4">
         <v>2</v>
       </c>
-      <c r="O4" s="4"/>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
       <c r="P4" s="4">
         <v>0</v>
       </c>
@@ -1328,13 +1361,13 @@
         <v>110</v>
       </c>
       <c r="W4" s="4">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="X4" s="4">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Y4" s="4">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Z4" s="4">
         <v>110</v>
@@ -1342,13 +1375,23 @@
       <c r="AA4" s="4">
         <v>0</v>
       </c>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="4"/>
-      <c r="AF4" s="4"/>
+      <c r="AB4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>102</v>
+      </c>
+      <c r="AD4" s="4">
+        <v>104</v>
+      </c>
+      <c r="AE4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="4">
+        <v>0</v>
+      </c>
       <c r="AG4" s="9">
-        <v>1321</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1394,7 +1437,9 @@
       <c r="N5" s="4">
         <v>96</v>
       </c>
-      <c r="O5" s="4"/>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
       <c r="P5" s="4">
         <v>98</v>
       </c>
@@ -1420,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="X5" s="4">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="Y5" s="4">
         <v>0</v>
@@ -1431,13 +1476,23 @@
       <c r="AA5" s="4">
         <v>103</v>
       </c>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
-      <c r="AD5" s="4"/>
-      <c r="AE5" s="4"/>
-      <c r="AF5" s="4"/>
+      <c r="AB5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="4">
+        <v>95</v>
+      </c>
+      <c r="AD5" s="4">
+        <v>102</v>
+      </c>
+      <c r="AE5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="4">
+        <v>0</v>
+      </c>
       <c r="AG5" s="9">
-        <v>1248</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1483,7 +1538,9 @@
       <c r="N6" s="4">
         <v>104</v>
       </c>
-      <c r="O6" s="4"/>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
       <c r="P6" s="4">
         <v>108</v>
       </c>
@@ -1506,7 +1563,7 @@
         <v>119</v>
       </c>
       <c r="W6" s="4">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="X6" s="4">
         <v>0</v>
@@ -1520,13 +1577,23 @@
       <c r="AA6" s="4">
         <v>110</v>
       </c>
-      <c r="AB6" s="4"/>
-      <c r="AC6" s="4"/>
-      <c r="AD6" s="4"/>
-      <c r="AE6" s="4"/>
-      <c r="AF6" s="4"/>
+      <c r="AB6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4">
+        <v>118</v>
+      </c>
+      <c r="AD6" s="4">
+        <v>109</v>
+      </c>
+      <c r="AE6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="4">
+        <v>0</v>
+      </c>
       <c r="AG6" s="9">
-        <v>1698</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1572,7 +1639,9 @@
       <c r="N7" s="4">
         <v>118</v>
       </c>
-      <c r="O7" s="4"/>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
       <c r="P7" s="4">
         <v>132</v>
       </c>
@@ -1595,7 +1664,7 @@
         <v>108</v>
       </c>
       <c r="W7" s="4">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="X7" s="4">
         <v>0</v>
@@ -1609,13 +1678,23 @@
       <c r="AA7" s="4">
         <v>116</v>
       </c>
-      <c r="AB7" s="4"/>
-      <c r="AC7" s="4"/>
-      <c r="AD7" s="4"/>
-      <c r="AE7" s="4"/>
-      <c r="AF7" s="4"/>
+      <c r="AB7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="4">
+        <v>106</v>
+      </c>
+      <c r="AD7" s="4">
+        <v>89</v>
+      </c>
+      <c r="AE7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="4">
+        <v>0</v>
+      </c>
       <c r="AG7" s="9">
-        <v>1639</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1661,7 +1740,9 @@
       <c r="N8" s="4">
         <v>96</v>
       </c>
-      <c r="O8" s="4"/>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
       <c r="P8" s="4">
         <v>0</v>
       </c>
@@ -1684,7 +1765,7 @@
         <v>109</v>
       </c>
       <c r="W8" s="4">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="X8" s="4">
         <v>0</v>
@@ -1698,13 +1779,23 @@
       <c r="AA8" s="4">
         <v>110</v>
       </c>
-      <c r="AB8" s="4"/>
-      <c r="AC8" s="4"/>
-      <c r="AD8" s="4"/>
-      <c r="AE8" s="4"/>
-      <c r="AF8" s="4"/>
+      <c r="AB8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>106</v>
+      </c>
+      <c r="AD8" s="4">
+        <v>108</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="4">
+        <v>0</v>
+      </c>
       <c r="AG8" s="9">
-        <v>1349</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1750,7 +1841,9 @@
       <c r="N9" s="4">
         <v>13</v>
       </c>
-      <c r="O9" s="4"/>
+      <c r="O9" s="4">
+        <v>0</v>
+      </c>
       <c r="P9" s="4">
         <v>0</v>
       </c>
@@ -1773,7 +1866,7 @@
         <v>104</v>
       </c>
       <c r="W9" s="4">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="X9" s="4">
         <v>0</v>
@@ -1787,13 +1880,23 @@
       <c r="AA9" s="4">
         <v>110</v>
       </c>
-      <c r="AB9" s="4"/>
-      <c r="AC9" s="4"/>
-      <c r="AD9" s="4"/>
-      <c r="AE9" s="4"/>
-      <c r="AF9" s="4"/>
+      <c r="AB9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="4">
+        <v>93</v>
+      </c>
+      <c r="AD9" s="4">
+        <v>105</v>
+      </c>
+      <c r="AE9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="4">
+        <v>0</v>
+      </c>
       <c r="AG9" s="9">
-        <v>1375</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1839,7 +1942,9 @@
       <c r="N10" s="4">
         <v>0</v>
       </c>
-      <c r="O10" s="4"/>
+      <c r="O10" s="4">
+        <v>0</v>
+      </c>
       <c r="P10" s="4">
         <v>99</v>
       </c>
@@ -1862,13 +1967,13 @@
         <v>107</v>
       </c>
       <c r="W10" s="4">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="X10" s="4">
         <v>0</v>
       </c>
       <c r="Y10" s="4">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="Z10" s="4">
         <v>105</v>
@@ -1876,13 +1981,23 @@
       <c r="AA10" s="4">
         <v>0</v>
       </c>
-      <c r="AB10" s="4"/>
-      <c r="AC10" s="4"/>
-      <c r="AD10" s="4"/>
-      <c r="AE10" s="4"/>
-      <c r="AF10" s="4"/>
+      <c r="AB10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="4">
+        <v>110</v>
+      </c>
+      <c r="AE10" s="4">
+        <v>18</v>
+      </c>
+      <c r="AF10" s="4">
+        <v>0</v>
+      </c>
       <c r="AG10" s="9">
-        <v>1166</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1928,7 +2043,9 @@
       <c r="N11" s="4">
         <v>49</v>
       </c>
-      <c r="O11" s="4"/>
+      <c r="O11" s="4">
+        <v>0</v>
+      </c>
       <c r="P11" s="4">
         <v>85</v>
       </c>
@@ -1951,7 +2068,7 @@
         <v>106</v>
       </c>
       <c r="W11" s="4">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="X11" s="4">
         <v>0</v>
@@ -1965,13 +2082,23 @@
       <c r="AA11" s="4">
         <v>107</v>
       </c>
-      <c r="AB11" s="4"/>
-      <c r="AC11" s="4"/>
-      <c r="AD11" s="4"/>
-      <c r="AE11" s="4"/>
-      <c r="AF11" s="4"/>
+      <c r="AB11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="4">
+        <v>102</v>
+      </c>
+      <c r="AD11" s="4">
+        <v>87</v>
+      </c>
+      <c r="AE11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="4">
+        <v>0</v>
+      </c>
       <c r="AG11" s="9">
-        <v>1446</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -2017,7 +2144,9 @@
       <c r="N12" s="4">
         <v>112</v>
       </c>
-      <c r="O12" s="4"/>
+      <c r="O12" s="4">
+        <v>0</v>
+      </c>
       <c r="P12" s="4">
         <v>116</v>
       </c>
@@ -2054,13 +2183,23 @@
       <c r="AA12" s="4">
         <v>104</v>
       </c>
-      <c r="AB12" s="4"/>
-      <c r="AC12" s="4"/>
-      <c r="AD12" s="4"/>
-      <c r="AE12" s="4"/>
-      <c r="AF12" s="4"/>
+      <c r="AB12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="4">
+        <v>118</v>
+      </c>
+      <c r="AD12" s="4">
+        <v>118</v>
+      </c>
+      <c r="AE12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="4">
+        <v>0</v>
+      </c>
       <c r="AG12" s="9">
-        <v>1389</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -2106,7 +2245,9 @@
       <c r="N13" s="4">
         <v>72</v>
       </c>
-      <c r="O13" s="4"/>
+      <c r="O13" s="4">
+        <v>0</v>
+      </c>
       <c r="P13" s="4">
         <v>97</v>
       </c>
@@ -2129,7 +2270,7 @@
         <v>104</v>
       </c>
       <c r="W13" s="4">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="X13" s="4">
         <v>0</v>
@@ -2143,13 +2284,23 @@
       <c r="AA13" s="4">
         <v>129</v>
       </c>
-      <c r="AB13" s="4"/>
-      <c r="AC13" s="4"/>
-      <c r="AD13" s="4"/>
-      <c r="AE13" s="4"/>
-      <c r="AF13" s="4"/>
+      <c r="AB13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="4">
+        <v>117</v>
+      </c>
+      <c r="AD13" s="4">
+        <v>85</v>
+      </c>
+      <c r="AE13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="4">
+        <v>0</v>
+      </c>
       <c r="AG13" s="9">
-        <v>1344</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -2195,7 +2346,9 @@
       <c r="N14" s="4">
         <v>96</v>
       </c>
-      <c r="O14" s="4"/>
+      <c r="O14" s="4">
+        <v>0</v>
+      </c>
       <c r="P14" s="4">
         <v>107</v>
       </c>
@@ -2218,7 +2371,7 @@
         <v>104</v>
       </c>
       <c r="W14" s="4">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="X14" s="4">
         <v>0</v>
@@ -2232,13 +2385,23 @@
       <c r="AA14" s="4">
         <v>90</v>
       </c>
-      <c r="AB14" s="4"/>
-      <c r="AC14" s="4"/>
-      <c r="AD14" s="4"/>
-      <c r="AE14" s="4"/>
-      <c r="AF14" s="4"/>
+      <c r="AB14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="4">
+        <v>86</v>
+      </c>
+      <c r="AD14" s="4">
+        <v>104</v>
+      </c>
+      <c r="AE14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="4">
+        <v>0</v>
+      </c>
       <c r="AG14" s="9">
-        <v>1602</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -2284,7 +2447,9 @@
       <c r="N15" s="4">
         <v>109</v>
       </c>
-      <c r="O15" s="4"/>
+      <c r="O15" s="4">
+        <v>0</v>
+      </c>
       <c r="P15" s="4">
         <v>115</v>
       </c>
@@ -2313,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="Y15" s="4">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="Z15" s="4">
         <v>0</v>
@@ -2321,13 +2486,23 @@
       <c r="AA15" s="4">
         <v>121</v>
       </c>
-      <c r="AB15" s="4"/>
-      <c r="AC15" s="4"/>
-      <c r="AD15" s="4"/>
-      <c r="AE15" s="4"/>
-      <c r="AF15" s="4"/>
+      <c r="AB15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="4">
+        <v>129</v>
+      </c>
+      <c r="AE15" s="4">
+        <v>50</v>
+      </c>
+      <c r="AF15" s="4">
+        <v>0</v>
+      </c>
       <c r="AG15" s="9">
-        <v>1126</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -2373,7 +2548,9 @@
       <c r="N16" s="4">
         <v>99</v>
       </c>
-      <c r="O16" s="4"/>
+      <c r="O16" s="4">
+        <v>0</v>
+      </c>
       <c r="P16" s="4">
         <v>101</v>
       </c>
@@ -2396,7 +2573,7 @@
         <v>114</v>
       </c>
       <c r="W16" s="4">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="X16" s="4">
         <v>0</v>
@@ -2410,13 +2587,23 @@
       <c r="AA16" s="4">
         <v>115</v>
       </c>
-      <c r="AB16" s="4"/>
-      <c r="AC16" s="4"/>
-      <c r="AD16" s="4"/>
-      <c r="AE16" s="4"/>
-      <c r="AF16" s="4"/>
+      <c r="AB16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="4">
+        <v>103</v>
+      </c>
+      <c r="AD16" s="4">
+        <v>62</v>
+      </c>
+      <c r="AE16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="4">
+        <v>0</v>
+      </c>
       <c r="AG16" s="9">
-        <v>1683</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -2462,7 +2649,9 @@
       <c r="N17" s="4">
         <v>83</v>
       </c>
-      <c r="O17" s="4"/>
+      <c r="O17" s="4">
+        <v>0</v>
+      </c>
       <c r="P17" s="4">
         <v>0</v>
       </c>
@@ -2485,7 +2674,7 @@
         <v>126</v>
       </c>
       <c r="W17" s="4">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="X17" s="4">
         <v>0</v>
@@ -2499,13 +2688,23 @@
       <c r="AA17" s="4">
         <v>102</v>
       </c>
-      <c r="AB17" s="4"/>
-      <c r="AC17" s="4"/>
-      <c r="AD17" s="4"/>
-      <c r="AE17" s="4"/>
-      <c r="AF17" s="4"/>
+      <c r="AB17" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="4">
+        <v>113</v>
+      </c>
+      <c r="AD17" s="4">
+        <v>111</v>
+      </c>
+      <c r="AE17" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="4">
+        <v>0</v>
+      </c>
       <c r="AG17" s="9">
-        <v>1551</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -2551,7 +2750,9 @@
       <c r="N18" s="4">
         <v>109</v>
       </c>
-      <c r="O18" s="4"/>
+      <c r="O18" s="4">
+        <v>0</v>
+      </c>
       <c r="P18" s="4">
         <v>100</v>
       </c>
@@ -2574,13 +2775,13 @@
         <v>0</v>
       </c>
       <c r="W18" s="4">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="X18" s="4">
         <v>0</v>
       </c>
       <c r="Y18" s="4">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="Z18" s="4">
         <v>1</v>
@@ -2588,13 +2789,23 @@
       <c r="AA18" s="4">
         <v>107</v>
       </c>
-      <c r="AB18" s="4"/>
-      <c r="AC18" s="4"/>
-      <c r="AD18" s="4"/>
-      <c r="AE18" s="4"/>
-      <c r="AF18" s="4"/>
+      <c r="AB18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="4">
+        <v>111</v>
+      </c>
+      <c r="AD18" s="4">
+        <v>111</v>
+      </c>
+      <c r="AE18" s="4">
+        <v>24</v>
+      </c>
+      <c r="AF18" s="4">
+        <v>0</v>
+      </c>
       <c r="AG18" s="9">
-        <v>1275</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2640,7 +2851,9 @@
       <c r="N19" s="6">
         <v>1327</v>
       </c>
-      <c r="O19" s="6"/>
+      <c r="O19" s="6">
+        <v>0</v>
+      </c>
       <c r="P19" s="6">
         <v>1346</v>
       </c>
@@ -2663,13 +2876,13 @@
         <v>1787</v>
       </c>
       <c r="W19" s="6">
-        <v>1885</v>
+        <v>1540</v>
       </c>
       <c r="X19" s="6">
-        <v>199</v>
+        <v>111</v>
       </c>
       <c r="Y19" s="6">
-        <v>196</v>
+        <v>81</v>
       </c>
       <c r="Z19" s="6">
         <v>1466</v>
@@ -2677,13 +2890,23 @@
       <c r="AA19" s="6">
         <v>1625</v>
       </c>
-      <c r="AB19" s="6"/>
-      <c r="AC19" s="6"/>
-      <c r="AD19" s="6"/>
-      <c r="AE19" s="6"/>
-      <c r="AF19" s="6"/>
+      <c r="AB19" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="6">
+        <v>1461</v>
+      </c>
+      <c r="AD19" s="6">
+        <v>1644</v>
+      </c>
+      <c r="AE19" s="6">
+        <v>92</v>
+      </c>
+      <c r="AF19" s="6">
+        <v>0</v>
+      </c>
       <c r="AG19" s="10">
-        <v>24150</v>
+        <v>26799</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -2745,6 +2968,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2753,7 +2979,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.8492647058823528</v>
+        <v>3.107843137254902</v>
       </c>
     </row>
   </sheetData>
